--- a/docs/audit/website-schemes-placement-2026-09-09.xlsx
+++ b/docs/audit/website-schemes-placement-2026-09-09.xlsx
@@ -9,10 +9,12 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schemes listed on the site" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How this was validated" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="myScheme cross-check" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="myScheme — the 85" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How this was validated" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Schemes listed on the site'!$A$1:$I$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Schemes listed on the site'!$A$1:$J$141</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,14 +65,8 @@
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
     </font>
-    <font>
-      <name val="Noto Sans"/>
-      <b val="1"/>
-      <color rgb="FF1A1A1A"/>
-      <sz val="12"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -89,12 +85,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE7F4E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFBE9E9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE7F4E4"/>
+        <fgColor rgb="FFF4F4F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F0FA"/>
       </patternFill>
     </fill>
     <fill>
@@ -125,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -142,16 +148,25 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -164,7 +179,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -530,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I141"/>
+  <dimension ref="A1:J141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -542,6 +556,7 @@
     <col width="44" customWidth="1" min="7" max="7"/>
     <col width="66" customWidth="1" min="8" max="8"/>
     <col width="72" customWidth="1" min="9" max="9"/>
+    <col width="74" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -590,6 +605,11 @@
           <t>Source of validation</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Cross-check: myScheme.gov.in</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -635,6 +655,11 @@
           <t>Annual Report 2025-26, ch.3 §3.2 and Notes on Demands for Grants 2026-27, Demand No.93 27 place children in hazardous cleaning occupations inside the Pre-Matric SC scheme; this page duplicates it and is empty.</t>
         </is>
       </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Pre-Matric Scholarships to the Children of Those Engaged in Occupations Involving Cleaning and Prone to Health Hazards" — agrees with this sheet.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -650,7 +675,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/2998/</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -678,6 +703,11 @@
       <c r="I3" s="3" t="inlineStr">
         <is>
           <t>The record's own text names NSFDC as the lender. NSFDC's lending is reported in Annual Report 2025-26, ch.3 §3.34 as the corporation's activity, not as a Department scheme; no scheme line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Credit Based Schemes For SC - Term Loan (TL)" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -695,7 +725,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/aajeevika-microfinance-yojana/</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -723,6 +753,11 @@
       <c r="I4" s="3" t="inlineStr">
         <is>
           <t>The record's own text names NSFDC as the lender. NSFDC's lending is reported in Annual Report 2025-26, ch.3 §3.34 as the corporation's activity, not as a Department scheme; no scheme line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -740,7 +775,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/ashram-shalas/</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -768,6 +803,11 @@
       <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Record's own text: Ashram Shala is a State residential-school programme; 100% grant to NGOs to open schools. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -785,7 +825,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/assistance-for-skill-development-of-obcs-dnts-ebcs/</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -813,6 +853,11 @@
       <c r="I6" s="3" t="inlineStr">
         <is>
           <t>The record's own text names NBCFDC as the lender. NBCFDC's lending is reported in Annual Report 2025-26, ch.3 §3.36 as the corporation's activity, not as a Department scheme; no scheme line in Notes on Demands for Grants 2026-27, Demand No.93. The record itself says "NGOs seeking grants from NBCFDC".</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -830,7 +875,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/assistance-to-students-of-dnts-studying-in-self-financed-institutes/</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -858,6 +903,11 @@
       <c r="I7" s="3" t="inlineStr">
         <is>
           <t>Record's own text: a State DNT scholarship for self-financed institutes, benefit stated in State rupee terms. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -875,7 +925,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/atal-vayo-abhyuday-yojana-avyay/</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -903,6 +953,11 @@
       <c r="I8" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.14 (AVYAY, components A–F); Notes on Demands for Grants 2026-27, Demand No.93 18 and 31.</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -920,7 +975,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/award-of-stipend-to-vjnt-and-sbc-students-studying-in-iti/</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -948,6 +1003,11 @@
       <c r="I9" s="3" t="inlineStr">
         <is>
           <t>Record's own text: VJNT/SBC are the category names used by Maharashtra, not by the Union. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -965,7 +1025,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/awareness-camp-nbcfdc/</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -993,6 +1053,11 @@
       <c r="I10" s="3" t="inlineStr">
         <is>
           <t>The record's own text names NBCFDC as the lender. NBCFDC's lending is reported in Annual Report 2025-26, ch.3 §3.36 as the corporation's activity, not as a Department scheme; no scheme line in Notes on Demands for Grants 2026-27, Demand No.93. An outreach activity; the page is empty.</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1075,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/awareness-camps/</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1038,6 +1103,11 @@
       <c r="I11" s="3" t="inlineStr">
         <is>
           <t>The record's own text names NSKFDC as the lender. NSKFDC's lending is reported in Annual Report 2025-26, ch.3 §3.35 as the corporation's activity, not as a Department scheme; no scheme line in Notes on Demands for Grants 2026-27, Demand No.93. The record describes camps run with State Channelising Agencies.</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1125,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/awareness-program-and-grant/</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>To confirm</t>
         </is>
@@ -1083,6 +1153,11 @@
       <c r="I12" s="3" t="inlineStr">
         <is>
           <t>Two lines of text naming only "NGOs working for DNTs". No administering body stated anywhere in the record.</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1175,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/babu-jagjivan-ram-all-india-essay-competition-scheme/</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1128,6 +1203,11 @@
       <c r="I13" s="3" t="inlineStr">
         <is>
           <t>Babu Jagjivan Ram National Foundation is an autonomous body of the Department (its organisation pages are published on this site). The scheme is not separately cited in Annual Report 2025-26, ch.3; the page is empty.</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1225,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/babu-jagjivan-ram-chair-scheme/</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1173,6 +1253,11 @@
       <c r="I14" s="3" t="inlineStr">
         <is>
           <t>BJRNF scheme, as above. Not separately cited in Annual Report 2025-26, ch.3; the page is empty.</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1275,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/babu-jagjivan-ram-scheme-for-celebration-of-birth-death-anniversary-of-great-saints/</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1218,6 +1303,11 @@
       <c r="I15" s="3" t="inlineStr">
         <is>
           <t>BJRNF scheme, as above. Not separately cited in Annual Report 2025-26, ch.3; the page is empty.</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -1235,7 +1325,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/basti-development-scheme/</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1263,6 +1353,11 @@
       <c r="I16" s="3" t="inlineStr">
         <is>
           <t>Record's own text: a State DNT basti-development programme, sector given as "Social Remedies". Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -1310,6 +1405,11 @@
           <t>Annual Report 2025-26, ch.3 §3.4; Notes on Demands for Grants 2026-27, Demand No.93 8.04; PIB Year-End Review 2025. Same scheme as record 77.</t>
         </is>
       </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "National Overseas Scholarship For Scheduled Caste Etc. Candidates" — agrees with this sheet.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1325,7 +1425,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/central-sector-scholarship-of-top-class-education-for-sc-students/</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1353,6 +1453,11 @@
       <c r="I18" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.5; Notes on Demands for Grants 2026-27, Demand No.93 8.03; PIB Year-End Review 2025.</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Education Loan Scheme" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1475,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/centrally-sponsored-scheme-for-implementation-of-the-protection-of-civil-rights-act-1955-and-the-scheduled-castes-and-the-scheduled-tribes-prevention-of-atrocities-act-1989/</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1398,6 +1503,11 @@
       <c r="I19" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.9; Notes on Demands for Grants 2026-27, Demand No.93 29; PIB Year-End Review 2025.</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Centrally Sponsored Scheme for Implementation of the Protection of Civil Rights Act, 1955 and the Scheduled Castes and the Scheduled Tribes (Prevention of Atrocities) Act, 1989" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1525,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/changes-in-the-centrally-sponsored-scheme-of-pre-matric-scholarship-to-children-of-those-engaged-in-unclean-occupations/</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1443,6 +1553,11 @@
       <c r="I20" s="3" t="inlineStr">
         <is>
           <t>The title is an amendment to a scheme, i.e. a circular; the body is empty.</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1575,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/civil-service-incentive-scheme/</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1488,6 +1603,11 @@
       <c r="I21" s="3" t="inlineStr">
         <is>
           <t>Record's own text: the record names MP State Civil Service. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1625,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/cm-housing-rent-scheme/</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1533,6 +1653,11 @@
       <c r="I22" s="3" t="inlineStr">
         <is>
           <t>Record's own text: a Chief Minister's housing-rent scheme for DNT college students. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1675,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/commencement-managment-of-ashram-schools/</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1578,6 +1703,11 @@
       <c r="I23" s="3" t="inlineStr">
         <is>
           <t>Record's own text: Ashram schools, Classes 1-5, a State programme. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1725,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/construction-of-hostels-for-obc-boys-and-girls/</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>Yes — a component of another scheme</t>
         </is>
@@ -1623,6 +1753,11 @@
       <c r="I24" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.22; Notes on Demands for Grants 2026-27, Demand No.93 30.03 — the hostel component of PM-YASASVI, not a scheme of its own.</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Construction of Hostels for OBC Boys and Girls" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1775,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/credit-enhancement-guarantee-scheme-for-the-scheduled-castes-scs/</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>To confirm</t>
         </is>
@@ -1668,6 +1803,11 @@
       <c r="I25" s="3" t="inlineStr">
         <is>
           <t>Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93. Present on the legacy socialjustice.gov.in site only.</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Credit Enhancement Guarantee Scheme For The Scheduled Castes" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1825,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/data-of-central-assistance-released-to-states-uts-for-last-5-years-i-e-2020-21-to-2024-25-along-with-no-of-atrocity-victims-and-no-of-couples-provided-incentives/</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1713,6 +1853,11 @@
       <c r="I26" s="3" t="inlineStr">
         <is>
           <t>The record's own title is a status/achievement table and the body is empty.</t>
+        </is>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1875,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/district-level-prizes-for-public-examination-10th-and-12th/</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1758,6 +1903,11 @@
       <c r="I27" s="3" t="inlineStr">
         <is>
           <t>Record's own text: BC/MBC categories and "Tamil as first language" — Tamil Nadu. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="inlineStr">
+        <is>
+          <t>Listed as a scheme of Tamil Nadu — myscheme.gov.in/schemes/psslp, Backward Classes, MBC and Minorities Welfare Department, Tamil Nadu — confirms it is a State scheme, not the Department's.</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1925,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/dnt-employment-scheme/</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1803,6 +1953,11 @@
       <c r="I28" s="3" t="inlineStr">
         <is>
           <t>Record's own text: a State BPL employment scheme for DNTs. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -1850,6 +2005,11 @@
           <t>Annual Report 2025-26, ch.3 §3.6; Notes on Demands for Grants 2026-27, Demand No.93 8.02. Same scheme as record 45, under the DACE name.</t>
         </is>
       </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Free Coaching Scheme" — agrees with this sheet.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1865,7 +2025,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/dr-ambedkar-chairs-revised-in-2022-2/</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D30" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1893,6 +2053,11 @@
       <c r="I30" s="3" t="inlineStr">
         <is>
           <t>Dr. Ambedkar Foundation is a body of the Department (Annual Report 2025-26, ch.3 §3.31). This scheme is not separately cited in ch.3; the record itself is a DAF scheme page.</t>
+        </is>
+      </c>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -1910,7 +2075,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/dr-ambedkar-foundation-national-essay-competition-scheme-2/</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1938,6 +2103,11 @@
       <c r="I31" s="3" t="inlineStr">
         <is>
           <t>DAF scheme, as above; not separately cited in Annual Report 2025-26, ch.3 ch.3.</t>
+        </is>
+      </c>
+      <c r="J31" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -1955,7 +2125,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/dr-ambedkar-international-centre-2/</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1983,6 +2153,11 @@
       <c r="I32" s="3" t="inlineStr">
         <is>
           <t>An institution, not a programme. The site already publishes DAIC organisation pages (organisation.json, slug dr-ambedkar-international-centre).</t>
+        </is>
+      </c>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2175,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/dr-ambedkar-medical-aid-scheme/</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2028,6 +2203,11 @@
       <c r="I33" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.31; PIB Year-End Review 2025.</t>
+        </is>
+      </c>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2225,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/dr-ambedkar-national-memorial-2/</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2073,6 +2253,11 @@
       <c r="I34" s="3" t="inlineStr">
         <is>
           <t>A memorial with visiting hours. Not a programme; no budget line.</t>
+        </is>
+      </c>
+      <c r="J34" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2275,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/dr-ambedkar-national-merit-award-for-meritorious-students-of-secondary-examination-belonging-to-scheduled-castes-and-scheduled-tribes-2/</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D35" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2118,6 +2303,11 @@
       <c r="I35" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.31 (Dr. Ambedkar National Merit Awards); PIB Year-End Review 2025.</t>
+        </is>
+      </c>
+      <c r="J35" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2325,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/dr-ambedkar-national-merit-award-scheme-for-meritorious-students-of-senior-secondary-school-examination-belonging-to-scheduled-caste-2/</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2163,6 +2353,11 @@
       <c r="I36" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.31 (Dr. Ambedkar National Merit Awards); PIB Year-End Review 2025.</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Centrally Sponsored Scheme of Upgradation of Merit of Scheduled Caste Students" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2375,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/dr-ambedkar-scheme-for-celebration-of-birth-death-anniversary-of-great-saints-revised-in-2022-2/</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D37" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2208,6 +2403,11 @@
       <c r="I37" s="3" t="inlineStr">
         <is>
           <t>DAF scheme; not separately cited in Annual Report 2025-26, ch.3 ch.3.</t>
+        </is>
+      </c>
+      <c r="J37" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2425,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/dr-ambedkar-scheme-for-social-integration-through-inter-caste-marriages-dr-ambedkar-national-relief-to-the-scheduled-castes-scheduled-tribes-victims-of-atrocities-2/</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D38" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2253,6 +2453,11 @@
       <c r="I38" s="3" t="inlineStr">
         <is>
           <t>DAF scheme; not separately cited in Annual Report 2025-26, ch.3 ch.3. Overlaps the inter-caste-marriage incentive inside Annual Report 2025-26, ch.3 §3.9.</t>
+        </is>
+      </c>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2475,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/dr-ambedkar-scheme-of-interest-subsidy-on-educational-loan-for-overseas-studies-for-obcs-ebcs/</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D39" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2298,6 +2503,11 @@
       <c r="I39" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.24; Notes on Demands for Grants 2026-27, Demand No.93 13.02.</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Dr Ambedkar Central Sector Scheme of Interest Subsidy on Educational Loans for Overseas Studies for Other Backward Classes (OBCs) and Economically Backward Classes (EBCs)" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2525,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/education-loan-el/</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2343,6 +2553,11 @@
       <c r="I40" s="3" t="inlineStr">
         <is>
           <t>The record's own text names NSKFDC as the lender. NSKFDC's lending is reported in Annual Report 2025-26, ch.3 §3.35 as the corporation's activity, not as a Department scheme; no scheme line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Loan Based Schemes For Safai Karamchari - Education Loan" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2575,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/educational-loan-schemeels/</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2388,6 +2603,11 @@
       <c r="I41" s="3" t="inlineStr">
         <is>
           <t>The record's own text names NBCFDC as the lender. NBCFDC's lending is reported in Annual Report 2025-26, ch.3 §3.36 as the corporation's activity, not as a Department scheme; no scheme line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J41" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2625,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/elderline/</t>
         </is>
       </c>
-      <c r="D42" s="9" t="inlineStr">
+      <c r="D42" s="12" t="inlineStr">
         <is>
           <t>Yes — a component of another scheme</t>
         </is>
@@ -2433,6 +2653,11 @@
       <c r="I42" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.14 D; PIB Year-End Review 2025.</t>
+        </is>
+      </c>
+      <c r="J42" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2675,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/excellent-award-scheme-for-social-workers/</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2478,6 +2703,11 @@
       <c r="I43" s="3" t="inlineStr">
         <is>
           <t>Record's own text: the record names MP residents. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2725,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/financial-assistance-to-the-students-who-studied-10th-standard-in-government-schools-and-pursuing-hsc-in-the-best-private-schools/</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2523,6 +2753,11 @@
       <c r="I44" s="3" t="inlineStr">
         <is>
           <t>Record's own text: the record names private schools in Tamil Nadu. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2775,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/financial-physical-achievements-of-last-five-years-upto-31-03-2018-under-loan-schemes-of-nskfdc/</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2568,6 +2803,11 @@
       <c r="I45" s="3" t="inlineStr">
         <is>
           <t>The record's own title is a status/achievement table and the body is empty. Its own period ends 31.03.2018.</t>
+        </is>
+      </c>
+      <c r="J45" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2825,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/free-coaching-for-scs-obcs-and-beneficiaries-of-pm-cares-children-scheme/</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D46" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2613,6 +2853,11 @@
       <c r="I46" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.6; Notes on Demands for Grants 2026-27, Demand No.93 8.02; PIB Year-End Review 2025.</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Free Coaching for SCs, OBCs and beneficiaries of PM CARES Children Scheme" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -2630,7 +2875,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/free-education-for-3-year-polytechnic-courses/</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2658,6 +2903,11 @@
       <c r="I47" s="3" t="inlineStr">
         <is>
           <t>Record's own text: BC/MBC polytechnic fee waiver — Tamil Nadu. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="inlineStr">
+        <is>
+          <t>Listed as a scheme of Tamil Nadu — myscheme.gov.in/schemes/fesftydpc — confirms it is a State scheme, not the Department's.</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2925,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/free-education-in-professional-courses/</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2703,6 +2953,11 @@
       <c r="I48" s="3" t="inlineStr">
         <is>
           <t>Record's own text: OBC/MBC/DNT, first-generation graduates — MBC is a Tamil Nadu category. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J48" s="9" t="inlineStr">
+        <is>
+          <t>Listed as a scheme of Tamil Nadu — myscheme.gov.in/schemes/fesfpc — confirms it is a State scheme, not the Department's.</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2975,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/free-education-in-undergraduate-colleges/</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2748,6 +3003,11 @@
       <c r="I49" s="3" t="inlineStr">
         <is>
           <t>Record's own text: OBC/MBC/DNT undergraduates in government colleges — Tamil Nadu. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J49" s="9" t="inlineStr">
+        <is>
+          <t>Listed as a scheme of Tamil Nadu — myscheme.gov.in/schemes/fes — confirms it is a State scheme, not the Department's.</t>
         </is>
       </c>
     </row>
@@ -2765,7 +3025,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/gadia-lohar-scheme/</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2793,6 +3053,11 @@
       <c r="I50" s="3" t="inlineStr">
         <is>
           <t>Record's own text: Gadia Lohar is a Rajasthan De-notified community. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J50" s="9" t="inlineStr">
+        <is>
+          <t>Listed as a scheme of Rajasthan — myscheme.gov.in/schemes/glrmy says "native of Rajasthan" — confirms it is a State scheme, not the Department's.</t>
         </is>
       </c>
     </row>
@@ -2810,7 +3075,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/general-term-loan-tl/</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2838,6 +3103,11 @@
       <c r="I51" s="3" t="inlineStr">
         <is>
           <t>The record's own text names NSKFDC as the lender. NSKFDC's lending is reported in Annual Report 2025-26, ch.3 §3.35 as the corporation's activity, not as a Department scheme; no scheme line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Loan Based Schemes For Safai Karamchari - General Term Loan (GTL)" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -2885,6 +3155,11 @@
           <t>Annual Report 2025-26, ch.3 §3.14 F. Same scheme as record 86.</t>
         </is>
       </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "PM-Special Training of Geriatric Caregivers" — agrees with this sheet.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -2900,7 +3175,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/girls-literacy-promotion-scheme-class-11th/</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2928,6 +3203,11 @@
       <c r="I53" s="3" t="inlineStr">
         <is>
           <t>Record's own text: Madhya Pradesh DNT girls' scholarship. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J53" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -2945,7 +3225,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/green-business-scheme/</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2973,6 +3253,11 @@
       <c r="I54" s="3" t="inlineStr">
         <is>
           <t>The record's own text names NSKFDC as the lender. NSKFDC's lending is reported in Annual Report 2025-26, ch.3 §3.35 as the corporation's activity, not as a Department scheme; no scheme line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Green Business Scheme" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -2990,7 +3275,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/group-loan-scheme/</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3018,6 +3303,11 @@
       <c r="I55" s="3" t="inlineStr">
         <is>
           <t>The record's own text names NBCFDC as the lender. NBCFDC's lending is reported in Annual Report 2025-26, ch.3 §3.36 as the corporation's activity, not as a Department scheme; no scheme line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J55" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -3035,7 +3325,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/guidelines-of-national-action-for-mechanized-sanitation-ecosystem-namaste-scheme-2/</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3063,6 +3353,11 @@
       <c r="I56" s="3" t="inlineStr">
         <is>
           <t>The record has a document title and an empty body — it is the document, not the programme.</t>
+        </is>
+      </c>
+      <c r="J56" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -3080,7 +3375,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/housing-plan/</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3108,6 +3403,11 @@
       <c r="I57" s="3" t="inlineStr">
         <is>
           <t>Record's own text: a State DNT housing plan. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J57" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3425,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/housing-scheme-for-scheduled-castes-and-dnts/</t>
         </is>
       </c>
-      <c r="D58" s="6" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3153,6 +3453,11 @@
       <c r="I58" s="3" t="inlineStr">
         <is>
           <t>Record's own text: a State housing scheme for SCs and DNTs. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J58" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3475,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/individual-loan-scheme/</t>
         </is>
       </c>
-      <c r="D59" s="6" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3198,6 +3503,11 @@
       <c r="I59" s="3" t="inlineStr">
         <is>
           <t>The record's own text names NBCFDC as the lender. NBCFDC's lending is reported in Annual Report 2025-26, ch.3 §3.36 as the corporation's activity, not as a Department scheme; no scheme line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "NBCFDC General Loan Scheme" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3525,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/infrastructure-for-nomadic-semi-nomadic-tribes-concrete-roads-and-drainage/</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3243,6 +3553,11 @@
       <c r="I60" s="3" t="inlineStr">
         <is>
           <t>Record's own text: State roads and drainage works in DNT settlements. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J60" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -3260,7 +3575,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/integrated-programme-for-senior-citizens-ipsrc/</t>
         </is>
       </c>
-      <c r="D61" s="9" t="inlineStr">
+      <c r="D61" s="12" t="inlineStr">
         <is>
           <t>Yes — a component of another scheme</t>
         </is>
@@ -3288,6 +3603,11 @@
       <c r="I61" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.14 A; Notes on Demands for Grants 2026-27, Demand No.93 31; PIB Year-End Review 2025.</t>
+        </is>
+      </c>
+      <c r="J61" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3625,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/itis-improvement-of-education-arts/</t>
         </is>
       </c>
-      <c r="D62" s="6" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3333,6 +3653,11 @@
       <c r="I62" s="3" t="inlineStr">
         <is>
           <t>Record's own text: the record names natives of MP. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J62" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published on myScheme under a State.</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3675,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/legal-aid-to-the-scheduled-castes-and-vimukta-jatis/</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr">
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3378,6 +3703,11 @@
       <c r="I63" s="3" t="inlineStr">
         <is>
           <t>Record's own text: a State legal-aid scheme for SCs and Vimukta Jatis. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J63" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3725,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/list-of-46-offences-under-the-sc-and-st-poa-act-1989/</t>
         </is>
       </c>
-      <c r="D64" s="6" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3423,6 +3753,11 @@
       <c r="I64" s="3" t="inlineStr">
         <is>
           <t>A list of offences under an Act. Reference material; the body is empty.</t>
+        </is>
+      </c>
+      <c r="J64" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3775,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/loan-schemes-flyer/</t>
         </is>
       </c>
-      <c r="D65" s="6" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3468,6 +3803,11 @@
       <c r="I65" s="3" t="inlineStr">
         <is>
           <t>The record's own text names NBCFDC as the lender. NBCFDC's lending is reported in Annual Report 2025-26, ch.3 §3.36 as the corporation's activity, not as a Department scheme; no scheme line in Notes on Demands for Grants 2026-27, Demand No.93. The record is a publicity flyer.</t>
+        </is>
+      </c>
+      <c r="J65" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3825,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/mahila-adhikarita-yojana-may/</t>
         </is>
       </c>
-      <c r="D66" s="6" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3513,6 +3853,11 @@
       <c r="I66" s="3" t="inlineStr">
         <is>
           <t>The record's own text names NSKFDC as the lender. NSKFDC's lending is reported in Annual Report 2025-26, ch.3 §3.35 as the corporation's activity, not as a Department scheme; no scheme line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J66" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -3530,7 +3875,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/mahila-samridhi-yojna-msy/</t>
         </is>
       </c>
-      <c r="D67" s="6" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3558,6 +3903,11 @@
       <c r="I67" s="3" t="inlineStr">
         <is>
           <t>The record's own text names NSKFDC as the lender. NSKFDC's lending is reported in Annual Report 2025-26, ch.3 §3.35 as the corporation's activity, not as a Department scheme; no scheme line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Mahila Samriddhi Yojana" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3925,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/maintenance-allowance-to-backward-class-students-under-training-in-sainik-schools/</t>
         </is>
       </c>
-      <c r="D68" s="6" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3603,6 +3953,11 @@
       <c r="I68" s="3" t="inlineStr">
         <is>
           <t>Record's own text: VJNT/SBC are the category names used by Maharashtra, not by the Union; Sainik School maintenance allowance. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3975,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/meritorious-scholarships-to-vjnt-and-sbc-students-studying-in-secondary-schools/</t>
         </is>
       </c>
-      <c r="D69" s="6" t="inlineStr">
+      <c r="D69" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3648,6 +4003,11 @@
       <c r="I69" s="3" t="inlineStr">
         <is>
           <t>Record's own text: VJNT/SBC are the category names used by Maharashtra, not by the Union. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="inlineStr">
+        <is>
+          <t>Listed as a scheme of Maharashtra — myscheme.gov.in/schemes/msvss — confirms it is a State scheme, not the Department's.</t>
         </is>
       </c>
     </row>
@@ -3665,7 +4025,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/micro-credit-finance-mcf/</t>
         </is>
       </c>
-      <c r="D70" s="6" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3693,6 +4053,11 @@
       <c r="I70" s="3" t="inlineStr">
         <is>
           <t>The record's own text names NSKFDC as the lender. NSKFDC's lending is reported in Annual Report 2025-26, ch.3 §3.35 as the corporation's activity, not as a Department scheme; no scheme line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J70" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -3710,7 +4075,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/micro-credit-finance-mcf-2/</t>
         </is>
       </c>
-      <c r="D71" s="6" t="inlineStr">
+      <c r="D71" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3738,6 +4103,11 @@
       <c r="I71" s="3" t="inlineStr">
         <is>
           <t>Empty page with the identical title to record 69 and "-2" appended to the web address.</t>
+        </is>
+      </c>
+      <c r="J71" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -3755,7 +4125,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/micro-finance-scheme/</t>
         </is>
       </c>
-      <c r="D72" s="6" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3783,6 +4153,11 @@
       <c r="I72" s="3" t="inlineStr">
         <is>
           <t>The record's own text names NSFDC as the lender. NSFDC's lending is reported in Annual Report 2025-26, ch.3 §3.34 as the corporation's activity, not as a Department scheme; no scheme line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J72" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Micro Credit Finance (NSFDC)" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -3800,7 +4175,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/mukhyamantri-vimukt-ghumantu-and-ardhghumantu-swarozgar-yojana-cm-self-employment-scheme/</t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="D73" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3828,6 +4203,11 @@
       <c r="I73" s="3" t="inlineStr">
         <is>
           <t>Record's own text: a Madhya Pradesh Chief Minister's self-employment scheme for DNTs. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J73" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -3845,7 +4225,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/national-action-for-mechanised-sanitation-ecosystem-namaste/</t>
         </is>
       </c>
-      <c r="D74" s="7" t="inlineStr">
+      <c r="D74" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3873,6 +4253,11 @@
       <c r="I74" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.11; Notes on Demands for Grants 2026-27, Demand No.93 17; PIB Year-End Review 2025.</t>
+        </is>
+      </c>
+      <c r="J74" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "National Action for Mechanised Sanitation Ecosystem (NAMASTE) - "Emergency Response Sanitation Unit (ERSU) Formation and Functionalisation"" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -3890,7 +4275,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/national-action-plan-for-drug-demand-reduction/</t>
         </is>
       </c>
-      <c r="D75" s="7" t="inlineStr">
+      <c r="D75" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3918,6 +4303,11 @@
       <c r="I75" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.15; Notes on Demands for Grants 2026-27, Demand No.93 32; PIB Year-End Review 2025.</t>
+        </is>
+      </c>
+      <c r="J75" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -3935,7 +4325,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/national-fellowship-for-obc-students-nf-obc/</t>
         </is>
       </c>
-      <c r="D76" s="7" t="inlineStr">
+      <c r="D76" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3963,6 +4353,11 @@
       <c r="I76" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.23; Notes on Demands for Grants 2026-27, Demand No.93 13.01.</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Central Sector Scheme of National Fellowship for Providing Fellowship to Scheduled Caste Students to Pursue M.Phil. &amp; PhD" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -3980,7 +4375,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/national-fellowship-for-scheduled-caste-students/</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr">
+      <c r="D77" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4008,6 +4403,11 @@
       <c r="I77" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.3; Notes on Demands for Grants 2026-27, Demand No.93 8.01; PIB Year-End Review 2025.</t>
+        </is>
+      </c>
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Central Sector Scheme of National Fellowship for Providing Fellowship to Scheduled Caste Students to Pursue M.Phil. &amp; PhD" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -4025,7 +4425,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/national-overseas-scholarship-nos-for-sc-etc-candidates/</t>
         </is>
       </c>
-      <c r="D78" s="7" t="inlineStr">
+      <c r="D78" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4053,6 +4453,11 @@
       <c r="I78" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.4; Notes on Demands for Grants 2026-27, Demand No.93 8.04; PIB Year-End Review 2025.</t>
+        </is>
+      </c>
+      <c r="J78" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "National Overseas Scholarship For Scheduled Caste Etc. Candidates" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4475,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/national-safai-karamcharis-finance-and-development-corporation-nskfdc/</t>
         </is>
       </c>
-      <c r="D79" s="6" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4098,6 +4503,11 @@
       <c r="I79" s="3" t="inlineStr">
         <is>
           <t>A corporation, not a programme. The site already publishes NSKFDC organisation pages (organisation.json).</t>
+        </is>
+      </c>
+      <c r="J79" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -4115,7 +4525,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/national-scheduled-castes-finance-and-development-corporation-nsfdc/</t>
         </is>
       </c>
-      <c r="D80" s="6" t="inlineStr">
+      <c r="D80" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4143,6 +4553,11 @@
       <c r="I80" s="3" t="inlineStr">
         <is>
           <t>A corporation, not a programme. The site already publishes NSFDC organisation pages (organisation.json).</t>
+        </is>
+      </c>
+      <c r="J80" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4575,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/other-initiatives/</t>
         </is>
       </c>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="D81" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4188,6 +4603,11 @@
       <c r="I81" s="3" t="inlineStr">
         <is>
           <t>The record's body is the text of a memorandum of understanding dated 26 June 2026.</t>
+        </is>
+      </c>
+      <c r="J81" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -4205,7 +4625,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/pandit-din-dayal-upadhyay-awas-yojana-housing-scheme/</t>
         </is>
       </c>
-      <c r="D82" s="6" t="inlineStr">
+      <c r="D82" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4233,6 +4653,11 @@
       <c r="I82" s="3" t="inlineStr">
         <is>
           <t>Record's own text: a State urban housing scheme with State assistance ceilings. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J82" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -4250,7 +4675,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/pay-use-toilets/</t>
         </is>
       </c>
-      <c r="D83" s="6" t="inlineStr">
+      <c r="D83" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4278,6 +4703,11 @@
       <c r="I83" s="3" t="inlineStr">
         <is>
           <t>The record's own text names NSKFDC as the lender. NSKFDC's lending is reported in Annual Report 2025-26, ch.3 §3.35 as the corporation's activity, not as a Department scheme; no scheme line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Loan based Scheme for Pay and Use Community Toilets" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -4295,7 +4725,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/payment-of-maintenance-allowance-to-vjnt-and-sbc-students-studying-in-professional-courses-and-living-in-hostel-attached-to-professional-colleges/</t>
         </is>
       </c>
-      <c r="D84" s="6" t="inlineStr">
+      <c r="D84" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4323,6 +4753,11 @@
       <c r="I84" s="3" t="inlineStr">
         <is>
           <t>Record's own text: VJNT/SBC are the category names used by Maharashtra, not by the Union. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J84" s="9" t="inlineStr">
+        <is>
+          <t>Listed as a scheme of Maharashtra — myscheme.gov.in/schemes/pmavssspc — confirms it is a State scheme, not the Department's.</t>
         </is>
       </c>
     </row>
@@ -4340,7 +4775,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/performance-linked-grants-in-aid-schemeplgia/</t>
         </is>
       </c>
-      <c r="D85" s="6" t="inlineStr">
+      <c r="D85" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4368,6 +4803,11 @@
       <c r="I85" s="3" t="inlineStr">
         <is>
           <t>Empty page. A performance-linked grant to the corporations' channelising agencies; no administering body stated.</t>
+        </is>
+      </c>
+      <c r="J85" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4825,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/pm-daksh/</t>
         </is>
       </c>
-      <c r="D86" s="7" t="inlineStr">
+      <c r="D86" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4413,6 +4853,11 @@
       <c r="I86" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.13; Notes on Demands for Grants 2026-27, Demand No.93 11 — and Notes on Demands for Grants 2026-27, Demand No.93 11 records the merger into PM Kaushal Vikas Yojana from 2026-27.</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Pradhan Mantri Dakshta Aur Kushalta Sampann Hitgrahi (PM-DAKSH)" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -4430,7 +4875,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/pm-special-training-of-geriatric-care-givers/</t>
         </is>
       </c>
-      <c r="D87" s="9" t="inlineStr">
+      <c r="D87" s="12" t="inlineStr">
         <is>
           <t>Yes — a component of another scheme</t>
         </is>
@@ -4458,6 +4903,11 @@
       <c r="I87" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.14 F; PIB Year-End Review 2025.</t>
+        </is>
+      </c>
+      <c r="J87" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "PM-Special Training of Geriatric Caregivers" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -4505,6 +4955,11 @@
           <t>Annual Report 2025-26, ch.3 §3.18-3.22; Notes on Demands for Grants 2026-27, Demand No.93 30. Same umbrella as record 88.</t>
         </is>
       </c>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "PM-YASASVI: Top Class School Education for OBC, EBC and DNT Students" — agrees with this sheet.</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -4520,7 +4975,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/pm-young-achievers-scholarship-award-scheme-for-vibrant-india-for-obcs-and-others-pm-yasasvi/</t>
         </is>
       </c>
-      <c r="D89" s="7" t="inlineStr">
+      <c r="D89" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4548,6 +5003,11 @@
       <c r="I89" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.18-3.22; Notes on Demands for Grants 2026-27, Demand No.93 30.01-30.05 — five sub-schemes.</t>
+        </is>
+      </c>
+      <c r="J89" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -4565,7 +5025,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/post-matric-scholarship/</t>
         </is>
       </c>
-      <c r="D90" s="6" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4593,6 +5053,11 @@
       <c r="I90" s="3" t="inlineStr">
         <is>
           <t>Record's own text: State scholarship rates and a State paying authority; the page also publishes a placeholder helpline, 1800-123-4567. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J90" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -4610,7 +5075,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/post-matric-scholarship-for-sc-students/</t>
         </is>
       </c>
-      <c r="D91" s="7" t="inlineStr">
+      <c r="D91" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4638,6 +5103,11 @@
       <c r="I91" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.1; Notes on Demands for Grants 2026-27, Demand No.93 26; PIB Year-End Review 2025.</t>
+        </is>
+      </c>
+      <c r="J91" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Centrally Sponsored Scheme of Post-Matric Scholarship for OBC Students for studying in India" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -4655,7 +5125,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/post-ssc-scholarship-for-boys/</t>
         </is>
       </c>
-      <c r="D92" s="6" t="inlineStr">
+      <c r="D92" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4683,6 +5153,11 @@
       <c r="I92" s="3" t="inlineStr">
         <is>
           <t>Record's own text: a State post-SSC scholarship; the income ceilings are a State's. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J92" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -4700,7 +5175,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/post-ssc-scholarship-to-girls/</t>
         </is>
       </c>
-      <c r="D93" s="6" t="inlineStr">
+      <c r="D93" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4728,6 +5203,11 @@
       <c r="I93" s="3" t="inlineStr">
         <is>
           <t>Record's own text: a State post-SSC scholarship for girls. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J93" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -4745,7 +5225,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/pradhan-mantri-anusuchit-jaati-abhyuday-yojna-pm-ajay/</t>
         </is>
       </c>
-      <c r="D94" s="7" t="inlineStr">
+      <c r="D94" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4773,6 +5253,11 @@
       <c r="I94" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.7; Notes on Demands for Grants 2026-27, Demand No.93 28; PIB Year-End Review 2025.</t>
+        </is>
+      </c>
+      <c r="J94" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Pradhan Mantri Anusuchit Jaati Abhyuday Yojana (PM-AJAY) - Adarsh Gram" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -4790,7 +5275,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/pre-matric-scholarships-scheme-for-scheduled-castes-others/</t>
         </is>
       </c>
-      <c r="D95" s="7" t="inlineStr">
+      <c r="D95" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4818,6 +5303,11 @@
       <c r="I95" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.2; Notes on Demands for Grants 2026-27, Demand No.93 27; PIB Year-End Review 2025.</t>
+        </is>
+      </c>
+      <c r="J95" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Pre- Matric Scholarships Scheme for Scheduled Castes &amp; Others" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -4835,7 +5325,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/pre-ssc-scholarship/</t>
         </is>
       </c>
-      <c r="D96" s="6" t="inlineStr">
+      <c r="D96" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4863,6 +5353,11 @@
       <c r="I96" s="3" t="inlineStr">
         <is>
           <t>Record's own text: a State pre-SSC scholarship with State income ceilings. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J96" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -4880,7 +5375,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/primary-education/</t>
         </is>
       </c>
-      <c r="D97" s="6" t="inlineStr">
+      <c r="D97" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4908,6 +5403,11 @@
       <c r="I97" s="3" t="inlineStr">
         <is>
           <t>Record's own text: a scholarship of Rs 15 a month paid through a State Directorate of Public Instruction. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J97" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published on myScheme under a State.</t>
         </is>
       </c>
     </row>
@@ -4925,7 +5425,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/publication-of-the-collected-works-of-baba-saheb-dr-b-r-ambedkar-cwba-in-hindi-english-and-other-regional-languages/</t>
         </is>
       </c>
-      <c r="D98" s="7" t="inlineStr">
+      <c r="D98" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4953,6 +5453,11 @@
       <c r="I98" s="3" t="inlineStr">
         <is>
           <t>A Dr. Ambedkar Foundation publication programme. Not cited as a scheme in Annual Report 2025-26, ch.3 ch.3; the page is a heading and nothing else.</t>
+        </is>
+      </c>
+      <c r="J98" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -4970,7 +5475,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/purchase-of-land-to-provide-accomodation-for-the-homeless/</t>
         </is>
       </c>
-      <c r="D99" s="6" t="inlineStr">
+      <c r="D99" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4998,6 +5503,11 @@
       <c r="I99" s="3" t="inlineStr">
         <is>
           <t>Record's own text: State land purchase for homeless DNT families. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J99" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -5015,7 +5525,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/rajarshi-chhatrapati-shahu-maharaj-merit-scholarship/</t>
         </is>
       </c>
-      <c r="D100" s="6" t="inlineStr">
+      <c r="D100" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5043,6 +5553,11 @@
       <c r="I100" s="3" t="inlineStr">
         <is>
           <t>Record's own text: VJNT/SBC are the category names used by Maharashtra, not by the Union; named for Rajarshi Shahu Maharaj. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J100" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5575,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/rashtriya-vayoshri-yojana-rvy/</t>
         </is>
       </c>
-      <c r="D101" s="9" t="inlineStr">
+      <c r="D101" s="12" t="inlineStr">
         <is>
           <t>Yes — a component of another scheme</t>
         </is>
@@ -5088,6 +5603,11 @@
       <c r="I101" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.14 C; Notes on Demands for Grants 2026-27, Demand No.93 18; PIB Year-End Review 2025.</t>
+        </is>
+      </c>
+      <c r="J101" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -5105,7 +5625,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/revised-guidelines-of-national-action-for-mechanized-sanitation-ecosystem-namaste-scheme/</t>
         </is>
       </c>
-      <c r="D102" s="6" t="inlineStr">
+      <c r="D102" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5133,6 +5653,11 @@
       <c r="I102" s="3" t="inlineStr">
         <is>
           <t>The record has a document title and an empty body — it is the document, not the programme.</t>
+        </is>
+      </c>
+      <c r="J102" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -5150,7 +5675,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/revised-scheme-guidelines-for-inclusion-of-waste-pickers-component-under-namaste/</t>
         </is>
       </c>
-      <c r="D103" s="6" t="inlineStr">
+      <c r="D103" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5178,6 +5703,11 @@
       <c r="I103" s="3" t="inlineStr">
         <is>
           <t>The record has a document title and an empty body — it is the document, not the programme.</t>
+        </is>
+      </c>
+      <c r="J103" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5725,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/sanitary-marts-scheme/</t>
         </is>
       </c>
-      <c r="D104" s="6" t="inlineStr">
+      <c r="D104" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5223,6 +5753,11 @@
       <c r="I104" s="3" t="inlineStr">
         <is>
           <t>The record's own text names NSKFDC as the lender. NSKFDC's lending is reported in Annual Report 2025-26, ch.3 §3.35 as the corporation's activity, not as a Department scheme; no scheme line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J104" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Loan Based Schemes For Safai Karamchari - Sanitary Marts Scheme" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5775,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/savitribai-phule-scholarship-for-vjnt-and-sbc-girl-students/</t>
         </is>
       </c>
-      <c r="D105" s="6" t="inlineStr">
+      <c r="D105" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5268,6 +5803,11 @@
       <c r="I105" s="3" t="inlineStr">
         <is>
           <t>Record's own text: VJNT/SBC are the category names used by Maharashtra, not by the Union. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J105" s="9" t="inlineStr">
+        <is>
+          <t>Listed as a scheme of Maharashtra — myscheme.gov.in/schemes/spsvsgs says "resident of the state of Maharashtra", applied on mahadbt.maharashtra.gov.in — confirms it is a State scheme, not the Department's.</t>
         </is>
       </c>
     </row>
@@ -5285,7 +5825,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/scheme-for-residential-education-for-students-in-high-schools-in-targeted-areas-shreshta/</t>
         </is>
       </c>
-      <c r="D106" s="7" t="inlineStr">
+      <c r="D106" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -5313,6 +5853,11 @@
       <c r="I106" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.10; Notes on Demands for Grants 2026-27, Demand No.93 9; PIB Year-End Review 2025.</t>
+        </is>
+      </c>
+      <c r="J106" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Education Loan Scheme" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5875,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/scheme-of-assistance-to-scheduled-castes-development-corporations-scdcs/</t>
         </is>
       </c>
-      <c r="D107" s="8" t="inlineStr">
+      <c r="D107" s="11" t="inlineStr">
         <is>
           <t>To confirm</t>
         </is>
@@ -5358,6 +5903,11 @@
       <c r="I107" s="3" t="inlineStr">
         <is>
           <t>Not among the 38 records in the scheme master. The record describes a 49:51 Centrally Sponsored share-capital scheme; no matching line found in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J107" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Scheme of Assistance to State Scheduled Castes Development Corporations" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -5375,7 +5925,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/scheme-of-national-awards-for-outstanding-services-in-the-field-of-prevention-of-alcoholism-and-substance-drug-abuse/</t>
         </is>
       </c>
-      <c r="D108" s="7" t="inlineStr">
+      <c r="D108" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -5403,6 +5953,11 @@
       <c r="I108" s="3" t="inlineStr">
         <is>
           <t>A Department award scheme in the drug-demand-reduction programme. Not separately cited in Annual Report 2025-26, ch.3 ch.3; the page is a documents table only.</t>
+        </is>
+      </c>
+      <c r="J108" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Scheme of Assistance for the Prevention of Alcoholism &amp; Substance (Drugs) Abuse and for Social Defence Services: General Grant-in-Aid Programme" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5975,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/schemes-implemented-by-national-safai-karamcharis-finance-development-corporation/</t>
         </is>
       </c>
-      <c r="D109" s="6" t="inlineStr">
+      <c r="D109" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5448,6 +6003,11 @@
       <c r="I109" s="3" t="inlineStr">
         <is>
           <t>Empty page. An index of another organisation's schemes.</t>
+        </is>
+      </c>
+      <c r="J109" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -5465,7 +6025,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/scholarship-for-pm-cares-children/</t>
         </is>
       </c>
-      <c r="D110" s="7" t="inlineStr">
+      <c r="D110" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -5493,6 +6053,11 @@
       <c r="I110" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.26; Notes on Demands for Grants 2026-27, Demand No.93 25 — the Department runs a special scholarship for PM CARES children.</t>
+        </is>
+      </c>
+      <c r="J110" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -5510,7 +6075,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/scholarship-for-technical-and-professional-courses/</t>
         </is>
       </c>
-      <c r="D111" s="6" t="inlineStr">
+      <c r="D111" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5538,6 +6103,11 @@
       <c r="I111" s="3" t="inlineStr">
         <is>
           <t>Record's own text: a State scholarship with State income ceilings. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J111" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -5555,7 +6125,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/scholarships-for-higher-education-for-young-achievers-scheme-shreyas-obc-others-2021-22-to-2025-26/</t>
         </is>
       </c>
-      <c r="D112" s="9" t="inlineStr">
+      <c r="D112" s="12" t="inlineStr">
         <is>
           <t>Yes — a component of another scheme</t>
         </is>
@@ -5583,6 +6153,11 @@
       <c r="I112" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.18-3.24; Notes on Demands for Grants 2026-27, Demand No.93 13.01-13.02 and 30.01-30.05. SHREYAS for OBCs is the family inside PM-YASASVI.</t>
+        </is>
+      </c>
+      <c r="J112" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Education Loan Scheme" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -5600,7 +6175,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/scholarships-for-post-matric-students/</t>
         </is>
       </c>
-      <c r="D113" s="6" t="inlineStr">
+      <c r="D113" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5628,6 +6203,11 @@
       <c r="I113" s="3" t="inlineStr">
         <is>
           <t>Record's own text: a State post-matric scholarship; "PUC" is a State's term. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J113" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -5645,7 +6225,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/seed-free-coaching/</t>
         </is>
       </c>
-      <c r="D114" s="7" t="inlineStr">
+      <c r="D114" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -5673,6 +6253,11 @@
       <c r="I114" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.30; Notes on Demands for Grants 2026-27, Demand No.93 14; PIB Year-End Review 2025.</t>
+        </is>
+      </c>
+      <c r="J114" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Free Coaching Scheme" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -5690,7 +6275,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/seed-health-insurance/</t>
         </is>
       </c>
-      <c r="D115" s="9" t="inlineStr">
+      <c r="D115" s="12" t="inlineStr">
         <is>
           <t>Yes — a component of another scheme</t>
         </is>
@@ -5718,6 +6303,11 @@
       <c r="I115" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.30 — SEED's health-insurance component, delivered through Ayushman Bharat.</t>
+        </is>
+      </c>
+      <c r="J115" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -5735,7 +6325,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/seed-housing/</t>
         </is>
       </c>
-      <c r="D116" s="9" t="inlineStr">
+      <c r="D116" s="12" t="inlineStr">
         <is>
           <t>Yes — a component of another scheme</t>
         </is>
@@ -5763,6 +6353,11 @@
       <c r="I116" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.30 — SEED's housing component, delivered through PM-AWAS.</t>
+        </is>
+      </c>
+      <c r="J116" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -5780,7 +6375,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/seed-livelihood/</t>
         </is>
       </c>
-      <c r="D117" s="9" t="inlineStr">
+      <c r="D117" s="12" t="inlineStr">
         <is>
           <t>Yes — a component of another scheme</t>
         </is>
@@ -5808,6 +6403,11 @@
       <c r="I117" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.30 — SEED's livelihood component, delivered through NRLM/NULM.</t>
+        </is>
+      </c>
+      <c r="J117" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -5825,7 +6425,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/self-employment-scheme-for-rehabilitation-of-manual-scavengers-srms-applicable-from-november-2013/</t>
         </is>
       </c>
-      <c r="D118" s="6" t="inlineStr">
+      <c r="D118" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5853,6 +6453,11 @@
       <c r="I118" s="3" t="inlineStr">
         <is>
           <t>Empty page carrying record 108's title and a third scheme's web address.</t>
+        </is>
+      </c>
+      <c r="J118" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -5870,7 +6475,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/self-employment-scheme-for-rehabilitation-of-manual-scavengers-srms-applicable-from-november-2013-3/</t>
         </is>
       </c>
-      <c r="D119" s="8" t="inlineStr">
+      <c r="D119" s="11" t="inlineStr">
         <is>
           <t>To confirm</t>
         </is>
@@ -5898,6 +6503,11 @@
       <c r="I119" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.11 records SRMS as subsumed into NAMASTE from 2023-24. The page is empty.</t>
+        </is>
+      </c>
+      <c r="J119" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Self Employment Scheme For Rehabilitation Of Manual Scavengers" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -5915,7 +6525,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/seniorcare-ageing-growth-engine-sage/</t>
         </is>
       </c>
-      <c r="D120" s="9" t="inlineStr">
+      <c r="D120" s="12" t="inlineStr">
         <is>
           <t>Yes — a component of another scheme</t>
         </is>
@@ -5943,6 +6553,11 @@
       <c r="I120" s="3" t="inlineStr">
         <is>
           <t>An AVYAY initiative. Not separately cited in Annual Report 2025-26, ch.3 §3.14 A-F; the record itself names AVYAY as its parent.</t>
+        </is>
+      </c>
+      <c r="J120" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -5960,7 +6575,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/skill-development-training-programmes-of-nskfdc-and-achievements/</t>
         </is>
       </c>
-      <c r="D121" s="6" t="inlineStr">
+      <c r="D121" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5988,6 +6603,11 @@
       <c r="I121" s="3" t="inlineStr">
         <is>
           <t>The record's own title is a status/achievement table and the body is empty.</t>
+        </is>
+      </c>
+      <c r="J121" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -6005,7 +6625,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/special-incentives-for-pre-matric-students/</t>
         </is>
       </c>
-      <c r="D122" s="6" t="inlineStr">
+      <c r="D122" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -6033,6 +6653,11 @@
       <c r="I122" s="3" t="inlineStr">
         <is>
           <t>Record's own text: a State pre-matric incentive. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J122" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6675,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/state-action-plan-for-senior-citizens-sapsrc/</t>
         </is>
       </c>
-      <c r="D123" s="9" t="inlineStr">
+      <c r="D123" s="12" t="inlineStr">
         <is>
           <t>Yes — a component of another scheme</t>
         </is>
@@ -6078,6 +6703,11 @@
       <c r="I123" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.14 — the AVYAY component funding State action plans under the Maintenance and Welfare of Parents and Senior Citizens Act 2007.</t>
+        </is>
+      </c>
+      <c r="J123" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -6095,7 +6725,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/state-scholarship-class-6th-to-10th/</t>
         </is>
       </c>
-      <c r="D124" s="6" t="inlineStr">
+      <c r="D124" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -6123,6 +6753,11 @@
       <c r="I124" s="3" t="inlineStr">
         <is>
           <t>Record's own text: Madhya Pradesh; paid through the Directorate of Public Instruction. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J124" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -6140,7 +6775,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/status-of-loan-application-for-rehabilitation-of-manual-scavengers/</t>
         </is>
       </c>
-      <c r="D125" s="6" t="inlineStr">
+      <c r="D125" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -6168,6 +6803,11 @@
       <c r="I125" s="3" t="inlineStr">
         <is>
           <t>The record's own title is a status/achievement table and the body is empty.</t>
+        </is>
+      </c>
+      <c r="J125" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6825,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/status-of-self-employment-scheme-for-rehabilitation-of-manual-scavengers-as-on-30-april2018/</t>
         </is>
       </c>
-      <c r="D126" s="6" t="inlineStr">
+      <c r="D126" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -6213,6 +6853,11 @@
       <c r="I126" s="3" t="inlineStr">
         <is>
           <t>The record's own title is a status/achievement table and the body is empty. Its own cut-off is 30 April 2018, for a scheme since subsumed.</t>
+        </is>
+      </c>
+      <c r="J126" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6875,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/support-for-marginalized-individuals-for-livelihood-and-enterprise-smile/</t>
         </is>
       </c>
-      <c r="D127" s="7" t="inlineStr">
+      <c r="D127" s="10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -6258,6 +6903,11 @@
       <c r="I127" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.16 and §3.17; Notes on Demands for Grants 2026-27, Demand No.93 15.01-15.02; PIB Year-End Review 2025.</t>
+        </is>
+      </c>
+      <c r="J127" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Support for Marginalized Individuals for Livelihood and Enterprise (SMILE): Composite Medical Health for Transgender Persons" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -6275,7 +6925,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/swachhta-udyami-yojana-suy/</t>
         </is>
       </c>
-      <c r="D128" s="6" t="inlineStr">
+      <c r="D128" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -6303,6 +6953,11 @@
       <c r="I128" s="3" t="inlineStr">
         <is>
           <t>The record's own text names NSKFDC as the lender. NSKFDC's lending is reported in Annual Report 2025-26, ch.3 §3.35 as the corporation's activity, not as a Department scheme; no scheme line in Notes on Demands for Grants 2026-27, Demand No.93. Also a NAMASTE component (Annual Report 2025-26, ch.3 §3.11).</t>
+        </is>
+      </c>
+      <c r="J128" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Loan Based Schemes For Safai Karamchari - Swachhta Udyami Yojana" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6975,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/talent-pool-scheme-for-dnts/</t>
         </is>
       </c>
-      <c r="D129" s="6" t="inlineStr">
+      <c r="D129" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -6348,6 +7003,11 @@
       <c r="I129" s="3" t="inlineStr">
         <is>
           <t>Record's own text: a State DNT talent scheme. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J129" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -6365,7 +7025,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/technology-upgradation-of-clusters/</t>
         </is>
       </c>
-      <c r="D130" s="8" t="inlineStr">
+      <c r="D130" s="11" t="inlineStr">
         <is>
           <t>To confirm</t>
         </is>
@@ -6393,6 +7053,11 @@
       <c r="I130" s="3" t="inlineStr">
         <is>
           <t>Empty page. No body, no administering organisation, no State — unattributable as it stands.</t>
+        </is>
+      </c>
+      <c r="J130" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -6410,7 +7075,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/top-class-education-in-colllege-for-obc-ebc-and-dnt-students/</t>
         </is>
       </c>
-      <c r="D131" s="9" t="inlineStr">
+      <c r="D131" s="12" t="inlineStr">
         <is>
           <t>Yes — a component of another scheme</t>
         </is>
@@ -6438,6 +7103,11 @@
       <c r="I131" s="3" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3 §3.21; Notes on Demands for Grants 2026-27, Demand No.93 30.04 — a PM-YASASVI sub-scheme.</t>
+        </is>
+      </c>
+      <c r="J131" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Education Loan Scheme" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -6455,7 +7125,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/training-of-motor-driving-to-vjnt-sbc-obcs/</t>
         </is>
       </c>
-      <c r="D132" s="6" t="inlineStr">
+      <c r="D132" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -6483,6 +7153,11 @@
       <c r="I132" s="3" t="inlineStr">
         <is>
           <t>Record's own text: VJNT/SBC are the category names used by Maharashtra, not by the Union. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J132" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -6500,7 +7175,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/tuition-fees-and-examination-fees-for-vjnt-sbc-students-studying-in-high-schools/</t>
         </is>
       </c>
-      <c r="D133" s="6" t="inlineStr">
+      <c r="D133" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -6528,6 +7203,11 @@
       <c r="I133" s="3" t="inlineStr">
         <is>
           <t>Record's own text: VJNT/SBC are the category names used by Maharashtra, not by the Union. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J133" s="9" t="inlineStr">
+        <is>
+          <t>Listed as a scheme of Maharashtra — myscheme.gov.in/schemes/tfefvssshs — confirms it is a State scheme, not the Department's.</t>
         </is>
       </c>
     </row>
@@ -6545,7 +7225,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/tution-fee-reimbusrment-scheme-of-sainik-school-public-schools/</t>
         </is>
       </c>
-      <c r="D134" s="6" t="inlineStr">
+      <c r="D134" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -6573,6 +7253,11 @@
       <c r="I134" s="3" t="inlineStr">
         <is>
           <t>Record's own text: a State fee-reimbursement scheme. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J134" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -6590,7 +7275,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/udyam-nidhi-yojana/</t>
         </is>
       </c>
-      <c r="D135" s="6" t="inlineStr">
+      <c r="D135" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -6618,6 +7303,11 @@
       <c r="I135" s="3" t="inlineStr">
         <is>
           <t>The record's own text names NSFDC as the lender. NSFDC's lending is reported in Annual Report 2025-26, ch.3 §3.34 as the corporation's activity, not as a Department scheme; no scheme line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J135" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
         </is>
       </c>
     </row>
@@ -6635,7 +7325,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/uniform-assistance-scheme/</t>
         </is>
       </c>
-      <c r="D136" s="6" t="inlineStr">
+      <c r="D136" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -6663,6 +7353,11 @@
       <c r="I136" s="3" t="inlineStr">
         <is>
           <t>Record's own text: a State uniform allowance of Rs 300. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J136" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -6680,7 +7375,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/upgadation-of-merit-of-sc-students/</t>
         </is>
       </c>
-      <c r="D137" s="8" t="inlineStr">
+      <c r="D137" s="11" t="inlineStr">
         <is>
           <t>To confirm</t>
         </is>
@@ -6708,6 +7403,11 @@
       <c r="I137" s="3" t="inlineStr">
         <is>
           <t>The record itself says the scheme was transferred from the Ministry of Human Resource Development in 1993-94. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J137" s="6" t="inlineStr">
+        <is>
+          <t>Listed under the Ministry as "Centrally Sponsored Scheme of Upgradation of Merit of Scheduled Caste Students" — agrees with this sheet.</t>
         </is>
       </c>
     </row>
@@ -6725,7 +7425,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/vimukt-jaati-basti-development-scheme/</t>
         </is>
       </c>
-      <c r="D138" s="6" t="inlineStr">
+      <c r="D138" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -6753,6 +7453,11 @@
       <c r="I138" s="3" t="inlineStr">
         <is>
           <t>Record's own text: a State DNT basti infrastructure scheme. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J138" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -6770,7 +7475,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/vimukt-jati-hostel-scheme/</t>
         </is>
       </c>
-      <c r="D139" s="6" t="inlineStr">
+      <c r="D139" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -6798,6 +7503,11 @@
       <c r="I139" s="3" t="inlineStr">
         <is>
           <t>Record's own text: VJNT/SBC are the category names used by Maharashtra, not by the Union. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J139" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -6815,7 +7525,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/vocational-training-for-vjnt-and-sbc-candidates-studying-in-government-industrial-training-institute/</t>
         </is>
       </c>
-      <c r="D140" s="6" t="inlineStr">
+      <c r="D140" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -6843,6 +7553,11 @@
       <c r="I140" s="3" t="inlineStr">
         <is>
           <t>Record's own text: VJNT/SBC are the category names used by Maharashtra, not by the Union. Not in Annual Report 2025-26, ch.3; no line in Notes on Demands for Grants 2026-27, Demand No.93.</t>
+        </is>
+      </c>
+      <c r="J140" s="9" t="inlineStr">
+        <is>
+          <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
     </row>
@@ -6860,7 +7575,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/workshops-job-fairs/</t>
         </is>
       </c>
-      <c r="D141" s="6" t="inlineStr">
+      <c r="D141" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -6890,9 +7605,14 @@
           <t>The record's own text names NSKFDC as the lender. NSKFDC's lending is reported in Annual Report 2025-26, ch.3 §3.35 as the corporation's activity, not as a Department scheme; no scheme line in Notes on Demands for Grants 2026-27, Demand No.93. Workshops and job fairs run by its channelising agencies.</t>
         </is>
       </c>
+      <c r="J141" s="8" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I141"/>
+  <autoFilter ref="A1:J141"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -7045,7 +7765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -7054,260 +7774,247 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>What is listed under Schemes &amp; Services on dosje.gov.in, read on 9 September 2026</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Verdict</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>Records</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>What it means</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n">
+      <c r="B4" s="15" t="n">
         <v>31</v>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>A scheme of this Department in its own right</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Yes — a component of another scheme</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>Real, but it belongs inside its umbrella (PM-YASASVI, SEED, AVYAY), not beside it</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Yes — but already listed under another name</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>The same scheme published twice</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>To confirm</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>Cannot be settled from published sources; needs the Department's answer</t>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Could not be settled from the Department's own published sources</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="15" t="n">
         <v>86</v>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>Not a scheme of this Department at all</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="16" t="n">
         <v>140</v>
       </c>
-      <c r="C9" s="12" t="inlineStr"/>
+      <c r="C9" s="16" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>Of the 86 that are not schemes</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>Records</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>Where they go</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>A State Government scheme</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n">
+      <c r="B13" s="15" t="n">
         <v>46</v>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>A labelled State-schemes directory under DWBDNC, every entry naming its State</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>A corporation 's loan product or activity</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n">
+      <c r="B14" s="15" t="n">
         <v>21</v>
       </c>
-      <c r="C14" s="12" t="inlineStr"/>
+      <c r="C14" s="15" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>A document</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n">
+      <c r="B15" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>Documents — Acts, Rules &amp; Guidelines, and Publications</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>A status or achievement table</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n">
+      <c r="B16" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>Dashboard / Statistics, or RTI suo-moto disclosure</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>An organisation or institution</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B17" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>Organisation pages, all four of which already exist on this site</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>A duplicate listing</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n">
+      <c r="B18" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>Delete, with a redirect</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>A reference list</t>
         </is>
       </c>
-      <c r="B19" s="12" t="n">
+      <c r="B19" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>Acts &amp; Rules, as an annexe to the PoA Act 1989</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>A memorandum of understanding</t>
         </is>
       </c>
-      <c r="B20" s="12" t="n">
+      <c r="B20" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>Documents — MoU</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>Short form used in the sheet</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>The document it refers to</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7320,118 +8027,1743 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="112" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>How every claim in this sheet was checked</t>
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>Checked against myScheme.gov.in, the National Government scheme portal, 9 September 2026</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>myScheme's ministry page lists 85 schemes under "Ministry Of Social Justice and Empowerment". Twenty of those are schemes of the Department of Empowerment of Persons with Disabilities, the other Department of the same Ministry — leaving 65 that belong to this Department and its corporations. That is the set this sheet was checked against.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Records</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>Listed on myScheme under the Ministry — agrees with this sheet</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="C6" s="15" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>Listed on myScheme under a State Government — confirms it is not the Department's</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="C7" s="15" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Not on myScheme in any form</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="n">
+        <v>91</v>
+      </c>
+      <c r="C8" s="15" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Where myScheme and this sheet disagree</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Ten records. Every one is a corporation loan product — Term Loan, Education Loan, GTL, Green Business, NBCFDC General Loan, Mahila Samriddhi, Micro Credit Finance, Pay &amp; Use Toilets, Sanitary Marts, Swachhta Udyami. myScheme publishes them as schemes of the Ministry; this sheet says they are products of the Department's corporations rather than schemes of the Department's own budget. Both are true. The disagreement is about the word "scheme", not about the facts: none of the ten carries a line in Demand No. 93, and all ten are administered by NSFDC, NSKFDC or NBCFDC. The placement recommendation is unchanged — they belong together under the corporations — but they should not be described to a citizen as though they were not schemes.</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="15" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>What myScheme settles that our own sources could not</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>Credit Enhancement Guarantee Scheme for the Scheduled Castes</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Published on myScheme under the Ministry. Treat as live, subject to the Department's confirmation.</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Scheme of Assistance to SC Development Corporations</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>Published on myScheme as "Scheme of Assistance to State Scheduled Castes Development Corporations". Treat as live.</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Upgradation of Merit of SC Students</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>Published on myScheme as a Centrally Sponsored Scheme. Treat as live.</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>Self Employment Scheme for Rehabilitation of Manual Scavengers (SRMS)</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>Still published on myScheme, although the Annual Report 2025-26 §3.11 records it as subsumed into NAMASTE from 2023-24. The two sources conflict; the Annual Report is the Department's own and should win.</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>What myScheme lists that our Schemes page does not carry at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>These are schemes of this Department, published on the National portal, and absent from the site's own list of 140 — while 86 things that are not the Department's schemes are on it.</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="15" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>VISVAS Yojana — interest subvention, for individuals and for self-help groups (Annual Report §3.25, Demand No. 93 line 10)</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="15" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>Venture Capital Fund for Scheduled Castes, and Ambedkar Social Innovation and Incubation Mission (ASIIM) (Annual Report §3.12, line 12)</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="n"/>
+      <c r="C22" s="15" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>Garima Greh — shelter homes for transgender persons, and SMILE's transgender sub-scheme as an entry of its own</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="n"/>
+      <c r="C23" s="15" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>Scheme for Supportive Money to the Parents of Transgender Children</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="n"/>
+      <c r="C24" s="15" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>Scheme of Grant-in-Aid to Voluntary and other Organizations Working for Scheduled Castes</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="n"/>
+      <c r="C25" s="15" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>Assistance to Voluntary Organizations Working for Welfare of OBCs</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="15" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>Centrally Sponsored Pre-matric and Post-Matric Scholarships for OBC students, and the Dr. Ambedkar Post-Matric Scholarship for EBC students, as entries of their own</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="n"/>
+      <c r="C27" s="15" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>I-MESA — Information, Monitoring, Evaluation and Social Audit, in four components</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="n"/>
+      <c r="C28" s="15" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>Rashtriya Parivar Sahayata Yojana</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="n"/>
+      <c r="C29" s="15" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>New Swarnima Scheme for Women, Vocational Education and Training Loan Scheme, and the NSFDC Internship Scheme</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n"/>
+      <c r="C30" s="15" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>What our sources carry that myScheme does not</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>myScheme lists none of the Dr. Ambedkar Foundation or Babu Jagjivan Ram National Foundation schemes, and none of AVYAY's senior-citizen components individually — no Elderline, no Integrated Programme for Senior Citizens, no Rashtriya Vayoshri Yojana as its own entry, no SAGE. Nor the National Action Plan for Drug Demand Reduction. Absence from myScheme is therefore not evidence that a scheme does not exist; it is evidence that the National portal's coverage of this Department is incomplete.</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="n"/>
+      <c r="C33" s="15" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C88"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>Every scheme myScheme publishes under "Ministry Of Social Justice and Empowerment", captured 9 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Scheme name on myScheme</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>Whose it is</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Persons With Disabilities Scheme In Colleges: Higher Education For Persons With Special Needs</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Empowerment of Persons with Disabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Centrally Sponsored Scheme of Pre-matric Scholarship to Other Backward Classes (OBC) for Studies in India</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Green Business Scheme</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>The NSFDC Internship Scheme</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Venture Capital Fund for Scheduled Castes</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Dr Ambedkar Central Sector Scheme of Interest Subsidy on Educational Loans for Overseas Studies for Other Backward Classes (OBCs) and Economically Backward Classes (EBCs)</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Pre-Matric Scholarship for Scheduled Caste Students</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Post Matric Scholarship Students With Disabilities</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Empowerment of Persons with Disabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Top Class Education For Scheduled Caste Students</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>Pre Matric Scholarship For Students With Disabilities</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Empowerment of Persons with Disabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Vanchit Ikai Samooh aur Vargon ki Aarthik Sahayata Yojana (VISVAS) for Individual</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>NBCFDC General Loan Scheme</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>Free Coaching for SCs, OBCs and beneficiaries of PM CARES Children Scheme</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>PM-YASASVI: Top Class School Education for OBC, EBC and DNT Students</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>PM-Special Training of Geriatric Caregivers</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>Support for Marginalized Individuals for Livelihood and Enterprise (SMILE): Composite Medical Health for Transgender Persons</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>Information, Monitoring, Evaluation and Social Audit (I-MESA): Project Monitoring Unit (PMU)</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>AVYAY - National Action Plan for Senior Citizens: Health and Shelter for Senior Citizens</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>Information-Monitoring, Evaluation, and Social Audit (I-MESA): Social Audit</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>Vikaas-Day Care Scheme For Person with Disability Children</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Empowerment of Persons with Disabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>Top Class Education For Students With Disabilities</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Empowerment of Persons with Disabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>National Overseas Scholarship For Scheduled Caste Etc. Candidates</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>National Overseas Scholarship For Students With Disabilities</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Empowerment of Persons with Disabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>Free Coaching for Students with Disabilities</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Empowerment of Persons with Disabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>Niramaya Health Insurance Scheme</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Empowerment of Persons with Disabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>Centrally Sponsored Scheme for Implementation of the Protection of Civil Rights Act, 1955 and the Scheduled Castes and the Scheduled Tribes (Prevention of Atrocities) Act, 1989</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>Scheme of Assistance to State Scheduled Castes Development Corporations</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>Ambedkar Social Innovation and Incubation Mission (ASIIM)</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>Disha - Early Intervention and School Readiness Scheme</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Empowerment of Persons with Disabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>Free Coaching Scheme</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>Pradhan Mantri Dakshta Aur Kushalta Sampann Hitgrahi (PM-DAKSH)</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>Loan Based Schemes For Safai Karamchari - Education Loan</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>Centrally Sponsored Scheme of Post-Matric Scholarship for OBC Students for studying in India</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="15" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>Central Sector Scheme of National Fellowship for Providing Fellowship to Scheduled Caste Students to Pursue M.Phil. &amp; PhD</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>Education Loan Scheme</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>PM-YASASVI: Post-Matric Scholarship for OBC, EBC and DNT Students</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>Garima Greh Shelter Homes For Transgender Persons</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>Vocational Education and Training Loan Scheme</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>Post-Matric Scholarship for SC students</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>National Action Plan for Skill Development of Persons with Disabilities</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Empowerment of Persons with Disabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>Scheme For Residential Education For Students in High Schools in Targeted Areas (SHRESHTA): Mode 1 - SHRESHTA Schools (Best CBSE Private Residential Schools)</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>Scheme For Residential Education For Students in High Schools in Targeted Areas (SHRESHTA): Mode 2 - NGO Operated Schools</t>
+        </is>
+      </c>
+      <c r="C45" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="15" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" s="15" t="inlineStr">
+        <is>
+          <t>Scholarships for Higher Education for Young Achievers Scheme (SHREYAS)  (OBC &amp; Others)</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="15" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" s="15" t="inlineStr">
+        <is>
+          <t>Samarth-Respite Care Scheme</t>
+        </is>
+      </c>
+      <c r="C47" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Empowerment of Persons with Disabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>Pre- Matric Scholarships Scheme for Scheduled Castes &amp; Others</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="15" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>New Swarnima Scheme For Women</t>
+        </is>
+      </c>
+      <c r="C49" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="15" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>Pre-Matric Scholarships to the Children of Those Engaged in Occupations Involving Cleaning and Prone to Health Hazards</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>National Fellowship for Students with Disabilities</t>
+        </is>
+      </c>
+      <c r="C51" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Empowerment of Persons with Disabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>Mahila Samriddhi Yojana</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="n">
+        <v>50</v>
+      </c>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>Centrally Sponsored Scheme of Upgradation of Merit of Scheduled Caste Students</t>
+        </is>
+      </c>
+      <c r="C53" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="15" t="n">
+        <v>51</v>
+      </c>
+      <c r="B54" s="15" t="inlineStr">
+        <is>
+          <t>Construction of Hostels for OBC Boys and Girls</t>
+        </is>
+      </c>
+      <c r="C54" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="15" t="n">
+        <v>52</v>
+      </c>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>PM-YASASVI: Pre-Matric Scholarship for OBC, EBC and DNT Students</t>
+        </is>
+      </c>
+      <c r="C55" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="15" t="n">
+        <v>53</v>
+      </c>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>SMILE - Comprehensive Rehabilitation For Welfare Of Transgender Persons</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="15" t="n">
+        <v>54</v>
+      </c>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>PM-YASASVI: Top Class College Education for OBC, EBC and DNT Students</t>
+        </is>
+      </c>
+      <c r="C57" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="15" t="n">
+        <v>55</v>
+      </c>
+      <c r="B58" s="15" t="inlineStr">
+        <is>
+          <t>Micro Credit Finance (NSFDC)</t>
+        </is>
+      </c>
+      <c r="C58" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="15" t="n">
+        <v>56</v>
+      </c>
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>Information, Monitoring, Evaluation and Social Audit (I-MESA): Evaluation and Studies</t>
+        </is>
+      </c>
+      <c r="C59" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="15" t="n">
+        <v>57</v>
+      </c>
+      <c r="B60" s="15" t="inlineStr">
+        <is>
+          <t>Scheme for Economic Empowerment of De-notified, Nomadic and Semi-Nomadic Tribes - "Educational Empowerment" Component</t>
+        </is>
+      </c>
+      <c r="C60" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="15" t="n">
+        <v>58</v>
+      </c>
+      <c r="B61" s="15" t="inlineStr">
+        <is>
+          <t>Gharaunda-Group Home for Adults Scheme</t>
+        </is>
+      </c>
+      <c r="C61" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Empowerment of Persons with Disabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="15" t="n">
+        <v>59</v>
+      </c>
+      <c r="B62" s="15" t="inlineStr">
+        <is>
+          <t>National Award for Individual Excellence</t>
+        </is>
+      </c>
+      <c r="C62" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="B63" s="15" t="inlineStr">
+        <is>
+          <t>Divyangjan Kaushal Yojana</t>
+        </is>
+      </c>
+      <c r="C63" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Empowerment of Persons with Disabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="15" t="n">
+        <v>61</v>
+      </c>
+      <c r="B64" s="15" t="inlineStr">
+        <is>
+          <t>Dr. Ambedakar Centrally Sponsored Scheme of Post-Matric Scholarships for the Economically Backward Class (EBC) Students</t>
+        </is>
+      </c>
+      <c r="C64" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="15" t="n">
+        <v>62</v>
+      </c>
+      <c r="B65" s="15" t="inlineStr">
+        <is>
+          <t>Assistance to Voluntary Organizations Working for Welfare of OBCs</t>
+        </is>
+      </c>
+      <c r="C65" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="15" t="n">
+        <v>63</v>
+      </c>
+      <c r="B66" s="15" t="inlineStr">
+        <is>
+          <t>Self Employment Scheme For Rehabilitation Of Manual Scavengers</t>
+        </is>
+      </c>
+      <c r="C66" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="15" t="n">
+        <v>64</v>
+      </c>
+      <c r="B67" s="15" t="inlineStr">
+        <is>
+          <t>Loan Based Schemes For Safai Karamchari - General Term Loan (GTL)</t>
+        </is>
+      </c>
+      <c r="C67" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="B68" s="15" t="inlineStr">
+        <is>
+          <t>Scheme for Supportive Money to the Parents of Transgender Children</t>
+        </is>
+      </c>
+      <c r="C68" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="15" t="n">
+        <v>66</v>
+      </c>
+      <c r="B69" s="15" t="inlineStr">
+        <is>
+          <t>Rashtriya Parivar Sahayata Yojana</t>
+        </is>
+      </c>
+      <c r="C69" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="15" t="n">
+        <v>67</v>
+      </c>
+      <c r="B70" s="15" t="inlineStr">
+        <is>
+          <t>Pradhan Mantri Adarsh Gram Yojana</t>
+        </is>
+      </c>
+      <c r="C70" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="15" t="n">
+        <v>68</v>
+      </c>
+      <c r="B71" s="15" t="inlineStr">
+        <is>
+          <t>National Awards For Empowerment Of Persons With Disabilities: Divyangjano Ke Liye Sarvshrestha Placement Agency</t>
+        </is>
+      </c>
+      <c r="C71" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Empowerment of Persons with Disabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="15" t="n">
+        <v>69</v>
+      </c>
+      <c r="B72" s="15" t="inlineStr">
+        <is>
+          <t>Scheme of Assistance for the Prevention of Alcoholism &amp; Substance (Drugs) Abuse and for Social Defence Services: General Grant-in-Aid Programme</t>
+        </is>
+      </c>
+      <c r="C72" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="15" t="n">
+        <v>70</v>
+      </c>
+      <c r="B73" s="15" t="inlineStr">
+        <is>
+          <t>Credit Enhancement Guarantee Scheme For The Scheduled Castes</t>
+        </is>
+      </c>
+      <c r="C73" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="15" t="n">
+        <v>71</v>
+      </c>
+      <c r="B74" s="15" t="inlineStr">
+        <is>
+          <t>Education Loan Scheme (NSFDC)</t>
+        </is>
+      </c>
+      <c r="C74" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="15" t="n">
+        <v>72</v>
+      </c>
+      <c r="B75" s="15" t="inlineStr">
+        <is>
+          <t>Information, Monitoring, Evaluation and Social Audit (I-MESA): Central Smart Surveillance Unit (CSSU)</t>
+        </is>
+      </c>
+      <c r="C75" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="15" t="n">
+        <v>73</v>
+      </c>
+      <c r="B76" s="15" t="inlineStr">
+        <is>
+          <t>Loan Based Schemes For Safai Karamchari - Sanitary Marts Scheme</t>
+        </is>
+      </c>
+      <c r="C76" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="15" t="n">
+        <v>74</v>
+      </c>
+      <c r="B77" s="15" t="inlineStr">
+        <is>
+          <t>Scheme Of Assistance To Disabled Persons For Purchase/Fitting Of Aids/Appliances</t>
+        </is>
+      </c>
+      <c r="C77" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Empowerment of Persons with Disabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="15" t="n">
+        <v>75</v>
+      </c>
+      <c r="B78" s="15" t="inlineStr">
+        <is>
+          <t>Pradhan Mantri Anusuchit Jaati Abhyuday Yojana (PM-AJAY) - Adarsh Gram</t>
+        </is>
+      </c>
+      <c r="C78" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="15" t="n">
+        <v>76</v>
+      </c>
+      <c r="B79" s="15" t="inlineStr">
+        <is>
+          <t>National Awards For Empowerment Of Persons With Disabilities: Sugamya Bharat Abhiyan</t>
+        </is>
+      </c>
+      <c r="C79" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Empowerment of Persons with Disabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="15" t="n">
+        <v>77</v>
+      </c>
+      <c r="B80" s="15" t="inlineStr">
+        <is>
+          <t>Loan Based Schemes For Safai Karamchari - Swachhta Udyami Yojana</t>
+        </is>
+      </c>
+      <c r="C80" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="15" t="n">
+        <v>78</v>
+      </c>
+      <c r="B81" s="15" t="inlineStr">
+        <is>
+          <t>Credit Based Schemes For SC - Term Loan (TL)</t>
+        </is>
+      </c>
+      <c r="C81" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="15" t="n">
+        <v>79</v>
+      </c>
+      <c r="B82" s="15" t="inlineStr">
+        <is>
+          <t>National Awards For Empowerment Of Persons With Disabilities: Divyangjano Ke Liye Sarvshrestha Niyoktha</t>
+        </is>
+      </c>
+      <c r="C82" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Empowerment of Persons with Disabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="15" t="n">
+        <v>80</v>
+      </c>
+      <c r="B83" s="15" t="inlineStr">
+        <is>
+          <t>National Awards For Empowerment Of Persons With Disabilities: Sarveshrestha Sansthan (Private Organization, NGO)</t>
+        </is>
+      </c>
+      <c r="C83" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Empowerment of Persons with Disabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="15" t="n">
+        <v>81</v>
+      </c>
+      <c r="B84" s="15" t="inlineStr">
+        <is>
+          <t>Scheme of Grant-in-Aid to Voluntary and other Organizations Working for Scheduled Castes</t>
+        </is>
+      </c>
+      <c r="C84" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="15" t="n">
+        <v>82</v>
+      </c>
+      <c r="B85" s="15" t="inlineStr">
+        <is>
+          <t>National Action for Mechanised Sanitation Ecosystem (NAMASTE) - "Emergency Response Sanitation Unit (ERSU) Formation and Functionalisation"</t>
+        </is>
+      </c>
+      <c r="C85" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="15" t="n">
+        <v>83</v>
+      </c>
+      <c r="B86" s="15" t="inlineStr">
+        <is>
+          <t>Deen Dayal Disabled Rehabilitation Scheme</t>
+        </is>
+      </c>
+      <c r="C86" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Empowerment of Persons with Disabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="15" t="n">
+        <v>84</v>
+      </c>
+      <c r="B87" s="15" t="inlineStr">
+        <is>
+          <t>Vanchit Ikai Samooh aur Vargon ki Aarthik Sahayata Yojana (VISVAS) for Self-Help Groups</t>
+        </is>
+      </c>
+      <c r="C87" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="15" t="n">
+        <v>85</v>
+      </c>
+      <c r="B88" s="15" t="inlineStr">
+        <is>
+          <t>Loan based Scheme for Pay and Use Community Toilets</t>
+        </is>
+      </c>
+      <c r="C88" s="15" t="inlineStr">
+        <is>
+          <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>How every claim in this workbook was checked</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Short form used in the sheet</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>The document it refers to</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Department of Social Justice and Empowerment, Annual Report 2025-26, Chapter 3 'Schemes &amp; Organizations' — socialjustice.gov.in/writereaddata/UploadFile/71441776233188.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Department of Social Justice and Empowerment, Annual Report 2025-26, Chapter 3 — socialjustice.gov.in/writereaddata/UploadFile/71441776233188.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Notes on Demands for Grants 2026-27, Demand No.93</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>Union Budget 2026-27, Notes on Demands for Grants, Demand No. 93, Department of Social Justice and Empowerment — indiabudget.gov.in/doc/eb/sbe93.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Union Budget 2026-27, Notes on Demands for Grants, Demand No. 93 — indiabudget.gov.in/doc/eb/sbe93.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>PIB Year-End Review 2025</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>Press Information Bureau release 2209488, 29 December 2025 — Overview of Schemes and Key Achievements of the Department</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Press Information Bureau release 2209488, 29 December 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>myScheme</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>myscheme.gov.in/search/ministry/Ministry Of Social Justice and Empowerment, and the individual scheme pages named in column J</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>organisation.json</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>apps/hub/src/content/website/organisation.json — the 228 organisation pages this site already publishes</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Record's own text</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>The body text of the page as published at the URL in column C, read on 9 September 2026</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="12" t="n"/>
-      <c r="B8" s="12" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>The two tests applied</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>A record was counted as a scheme of this Department only where it appears in Chapter 3 of the Annual Report 2025-26, or carries a line in Demand No. 93 of the Notes on Demands for Grants 2026-27, or is a published scheme of the Dr. Ambedkar Foundation or the Babu Jagjivan Ram National Foundation — both bodies of this Department.</t>
-        </is>
-      </c>
-    </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>A record was counted as a State scheme only where its own text shows it: the page names the State, or uses a category name that only one State uses (VJNT and SBC are Maharashtra's; MBC is Tamil Nadu's; Gadia Lohar is a Rajasthan community). Where the wording is a State's but the State is not named, column F says so rather than guessing.</t>
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>The tests applied</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Where a State is marked '(inferred)', the page does not name the State and the attribution rests on the category vocabulary alone. Those need the Department's confirmation before publication.</t>
-        </is>
-      </c>
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>A record was counted as a scheme of this Department only where it appears in Chapter 3 of the Annual Report 2025-26, or carries a line in Demand No. 93 of the Notes on Demands for Grants 2026-27, or is a published scheme of the Dr. Ambedkar Foundation or the Babu Jagjivan Ram National Foundation, both bodies of this Department.</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>This pass did not open the PDFs attached to each record, and did not test whether a scheme is still accepting applications. It reads what the site publishes.</t>
-        </is>
-      </c>
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>A record was counted as a State scheme only where its own text shows it: the page names the State, or uses a category name that only one State uses (VJNT and SBC are Maharashtra's; MBC is Tamil Nadu's; Gadia Lohar is a Rajasthan community). Nine of the 46 were then confirmed individually on myScheme, each published under a State — Maharashtra, Tamil Nadu or Rajasthan. None of the 46 appears in myScheme's list of Ministry schemes.</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>Where a State is marked '(inferred)', the page does not name the State and the attribution rests on category vocabulary alone. Those still need the Department's confirmation.</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Column J was matched by comparing scheme names. A match was accepted only at high similarity or where checked by hand; where the sheet says 'Not on myScheme in any form', that is the absence of a match, which is weaker evidence than a match — myScheme's coverage of this Department is itself incomplete (see the cross-check tab).</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>This pass did not open the PDFs attached to each record, and did not test whether a scheme is still accepting applications.</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/audit/website-schemes-placement-2026-09-09.xlsx
+++ b/docs/audit/website-schemes-placement-2026-09-09.xlsx
@@ -9,12 +9,15 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schemes listed on the site" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="myScheme cross-check" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="myScheme — the 85" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How this was validated" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Persona &amp; category tagging" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Persona x category grid" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Suggested extra filters" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="myScheme cross-check" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="myScheme — the 85" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How this was validated" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Schemes listed on the site'!$A$1:$J$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Schemes listed on the site'!$A$1:$L$141</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,6 +59,12 @@
     </font>
     <font>
       <name val="Noto Sans"/>
+      <i val="1"/>
+      <color rgb="FF1A1A1A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Noto Sans"/>
       <b val="1"/>
       <color rgb="FF1A1A1A"/>
       <sz val="14"/>
@@ -65,8 +74,14 @@
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
     </font>
+    <font>
+      <name val="Noto Sans"/>
+      <b val="1"/>
+      <color rgb="FF1A1A1A"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -113,6 +128,11 @@
         <fgColor rgb="FFF2F8F1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7F7F8"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -131,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -166,11 +186,17 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -178,6 +204,19 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -544,7 +583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J141"/>
+  <dimension ref="A1:L141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -557,6 +596,8 @@
     <col width="66" customWidth="1" min="8" max="8"/>
     <col width="72" customWidth="1" min="9" max="9"/>
     <col width="74" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
+    <col width="44" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -610,6 +651,16 @@
           <t>Cross-check: myScheme.gov.in</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Who it is for (persona)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>What it provides (category)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -660,6 +711,16 @@
           <t>Listed under the Ministry as "Pre-Matric Scholarships to the Children of Those Engaged in Occupations Involving Cleaning and Prone to Health Hazards" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Safai Karamcharis · Students</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -710,6 +771,16 @@
           <t>Listed under the Ministry as "Credit Based Schemes For SC - Term Loan (TL)" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled Castes</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -760,6 +831,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled Castes</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -810,6 +891,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes · Students</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Residential Schools, Hostels and Coaching</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -860,6 +951,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Other Backward Classes · De-notified, Nomadic and Semi-Nomadic Tribes · Voluntary Organisations</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Skill Training and Livelihood · Grants to Voluntary Organisations</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -910,6 +1011,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes · Students</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -960,6 +1071,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Senior Citizens · Voluntary Organisations</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Care, Shelter and Health · Skill Training and Livelihood · Protection, Relief and Grievance · Grants to Voluntary Organisations</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1010,6 +1131,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes · Students</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships · Skill Training and Livelihood</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1060,6 +1191,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Other Backward Classes</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1110,6 +1251,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Safai Karamcharis</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1160,6 +1311,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes · Voluntary Organisations</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Grants to Voluntary Organisations</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1210,6 +1371,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Awards and Recognition</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1260,6 +1431,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>— none (not citizen-facing)</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Awards and Recognition</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1310,6 +1491,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Voluntary Organisations</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Grants to Voluntary Organisations</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1360,6 +1551,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Housing and Settlement</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1410,6 +1611,16 @@
           <t>Listed under the Ministry as "National Overseas Scholarship For Scheduled Caste Etc. Candidates" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled Castes · De-notified, Nomadic and Semi-Nomadic Tribes · Students</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1460,6 +1671,16 @@
           <t>Listed under the Ministry as "Education Loan Scheme" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled Castes · Students</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1510,6 +1731,16 @@
           <t>Listed under the Ministry as "Centrally Sponsored Scheme for Implementation of the Protection of Civil Rights Act, 1955 and the Scheduled Castes and the Scheduled Tribes (Prevention of Atrocities) Act, 1989" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Victims of Atrocities · Scheduled Castes</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Protection, Relief and Grievance</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1560,6 +1791,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Safai Karamcharis · Students</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1610,6 +1851,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes · Students</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Awards and Recognition</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1660,6 +1911,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes · Students</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Housing and Settlement</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -1710,6 +1971,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes · Students</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Residential Schools, Hostels and Coaching</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1725,7 +1996,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/construction-of-hostels-for-obc-boys-and-girls/</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D24" s="14" t="inlineStr">
         <is>
           <t>Yes — a component of another scheme</t>
         </is>
@@ -1758,6 +2029,16 @@
       <c r="J24" s="6" t="inlineStr">
         <is>
           <t>Listed under the Ministry as "Construction of Hostels for OBC Boys and Girls" — agrees with this sheet.</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Other Backward Classes · Students</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Residential Schools, Hostels and Coaching</t>
         </is>
       </c>
     </row>
@@ -1810,6 +2091,16 @@
           <t>Listed under the Ministry as "Credit Enhancement Guarantee Scheme For The Scheduled Castes" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled Castes</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1860,6 +2151,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Victims of Atrocities · Scheduled Castes</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Protection, Relief and Grievance</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -1910,6 +2211,16 @@
           <t>Listed as a scheme of Tamil Nadu — myscheme.gov.in/schemes/psslp, Backward Classes, MBC and Minorities Welfare Department, Tamil Nadu — confirms it is a State scheme, not the Department's.</t>
         </is>
       </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Other Backward Classes · De-notified, Nomadic and Semi-Nomadic Tribes · Students</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Awards and Recognition</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1960,6 +2271,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>Skill Training and Livelihood</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -2010,6 +2331,16 @@
           <t>Listed under the Ministry as "Free Coaching Scheme" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled Castes · Other Backward Classes · Students</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Residential Schools, Hostels and Coaching</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -2060,6 +2391,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>— none (not citizen-facing)</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Awards and Recognition</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -2110,6 +2451,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Awards and Recognition</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -2160,6 +2511,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>— none (not citizen-facing)</t>
+        </is>
+      </c>
+      <c r="L32" s="13" t="inlineStr">
+        <is>
+          <t>— none (not a benefit)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -2210,6 +2571,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled Castes</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Care, Shelter and Health</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -2260,6 +2631,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>— none (not citizen-facing)</t>
+        </is>
+      </c>
+      <c r="L34" s="13" t="inlineStr">
+        <is>
+          <t>— none (not a benefit)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -2310,6 +2691,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled Castes · Students</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Awards and Recognition</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -2360,6 +2751,16 @@
           <t>Listed under the Ministry as "Centrally Sponsored Scheme of Upgradation of Merit of Scheduled Caste Students" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled Castes · Students</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Awards and Recognition</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -2410,6 +2811,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Voluntary Organisations</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Grants to Voluntary Organisations</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -2460,6 +2871,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled Castes · Victims of Atrocities</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Protection, Relief and Grievance</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -2510,6 +2931,16 @@
           <t>Listed under the Ministry as "Dr Ambedkar Central Sector Scheme of Interest Subsidy on Educational Loans for Overseas Studies for Other Backward Classes (OBCs) and Economically Backward Classes (EBCs)" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Other Backward Classes · Students</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -2560,6 +2991,16 @@
           <t>Listed under the Ministry as "Loan Based Schemes For Safai Karamchari - Education Loan" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Safai Karamcharis · Students</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -2610,6 +3051,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Other Backward Classes · Students</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -2625,7 +3076,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/elderline/</t>
         </is>
       </c>
-      <c r="D42" s="12" t="inlineStr">
+      <c r="D42" s="14" t="inlineStr">
         <is>
           <t>Yes — a component of another scheme</t>
         </is>
@@ -2658,6 +3109,16 @@
       <c r="J42" s="8" t="inlineStr">
         <is>
           <t>Not on myScheme in any form.</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>Senior Citizens</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>Care, Shelter and Health · Protection, Relief and Grievance</t>
         </is>
       </c>
     </row>
@@ -2710,6 +3171,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>Awards and Recognition</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -2760,6 +3231,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>Other Backward Classes · De-notified, Nomadic and Semi-Nomadic Tribes · Students</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -2810,6 +3291,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Safai Karamcharis</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -2860,6 +3351,16 @@
           <t>Listed under the Ministry as "Free Coaching for SCs, OBCs and beneficiaries of PM CARES Children Scheme" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled Castes · Other Backward Classes · Students</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>Residential Schools, Hostels and Coaching</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -2910,6 +3411,16 @@
           <t>Listed as a scheme of Tamil Nadu — myscheme.gov.in/schemes/fesftydpc — confirms it is a State scheme, not the Department's.</t>
         </is>
       </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>Other Backward Classes · De-notified, Nomadic and Semi-Nomadic Tribes · Students</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -2960,6 +3471,16 @@
           <t>Listed as a scheme of Tamil Nadu — myscheme.gov.in/schemes/fesfpc — confirms it is a State scheme, not the Department's.</t>
         </is>
       </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>Other Backward Classes · De-notified, Nomadic and Semi-Nomadic Tribes · Students</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -3010,6 +3531,16 @@
           <t>Listed as a scheme of Tamil Nadu — myscheme.gov.in/schemes/fes — confirms it is a State scheme, not the Department's.</t>
         </is>
       </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Other Backward Classes · De-notified, Nomadic and Semi-Nomadic Tribes · Students</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -3060,6 +3591,16 @@
           <t>Listed as a scheme of Rajasthan — myscheme.gov.in/schemes/glrmy says "native of Rajasthan" — confirms it is a State scheme, not the Department's.</t>
         </is>
       </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>Housing and Settlement</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -3110,6 +3651,16 @@
           <t>Listed under the Ministry as "Loan Based Schemes For Safai Karamchari - General Term Loan (GTL)" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>Safai Karamcharis</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -3160,6 +3711,16 @@
           <t>Listed under the Ministry as "PM-Special Training of Geriatric Caregivers" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>Senior Citizens</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>Skill Training and Livelihood</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -3210,6 +3771,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes · Students</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -3260,6 +3831,16 @@
           <t>Listed under the Ministry as "Green Business Scheme" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>Safai Karamcharis</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -3310,6 +3891,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>Other Backward Classes</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -3360,6 +3951,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>Safai Karamcharis</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>Care, Shelter and Health · Skill Training and Livelihood · Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -3410,6 +4011,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>Housing and Settlement</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -3460,6 +4071,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled Castes · De-notified, Nomadic and Semi-Nomadic Tribes</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>Housing and Settlement</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -3510,6 +4131,16 @@
           <t>Listed under the Ministry as "NBCFDC General Loan Scheme" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>Other Backward Classes</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -3560,6 +4191,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>Housing and Settlement</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -3575,7 +4216,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/integrated-programme-for-senior-citizens-ipsrc/</t>
         </is>
       </c>
-      <c r="D61" s="12" t="inlineStr">
+      <c r="D61" s="14" t="inlineStr">
         <is>
           <t>Yes — a component of another scheme</t>
         </is>
@@ -3608,6 +4249,16 @@
       <c r="J61" s="8" t="inlineStr">
         <is>
           <t>Not on myScheme in any form.</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>Senior Citizens · Voluntary Organisations</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>Care, Shelter and Health · Grants to Voluntary Organisations</t>
         </is>
       </c>
     </row>
@@ -3660,6 +4311,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published on myScheme under a State.</t>
         </is>
       </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>Skill Training and Livelihood</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -3710,6 +4371,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled Castes · De-notified, Nomadic and Semi-Nomadic Tribes</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>Protection, Relief and Grievance</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -3760,6 +4431,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>Victims of Atrocities · Scheduled Castes</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>Protection, Relief and Grievance</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -3810,6 +4491,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>Other Backward Classes</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -3860,6 +4551,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>Safai Karamcharis</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -3910,6 +4611,16 @@
           <t>Listed under the Ministry as "Mahila Samriddhi Yojana" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>Safai Karamcharis</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -3960,6 +4671,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>Other Backward Classes · De-notified, Nomadic and Semi-Nomadic Tribes · Students</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>Residential Schools, Hostels and Coaching</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -4010,6 +4731,16 @@
           <t>Listed as a scheme of Maharashtra — myscheme.gov.in/schemes/msvss — confirms it is a State scheme, not the Department's.</t>
         </is>
       </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes · Students</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -4060,6 +4791,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>Safai Karamcharis</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -4110,6 +4851,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>Safai Karamcharis</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -4160,6 +4911,16 @@
           <t>Listed under the Ministry as "Micro Credit Finance (NSFDC)" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled Castes</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -4210,6 +4971,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>Skill Training and Livelihood</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -4260,6 +5031,16 @@
           <t>Listed under the Ministry as "National Action for Mechanised Sanitation Ecosystem (NAMASTE) - "Emergency Response Sanitation Unit (ERSU) Formation and Functionalisation"" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>Safai Karamcharis</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>Care, Shelter and Health · Skill Training and Livelihood · Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -4310,6 +5091,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>Persons Affected by Substance Use · Voluntary Organisations</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>De-addiction and Counselling · Grants to Voluntary Organisations</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -4360,6 +5151,16 @@
           <t>Listed under the Ministry as "Central Sector Scheme of National Fellowship for Providing Fellowship to Scheduled Caste Students to Pursue M.Phil. &amp; PhD" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>Other Backward Classes · Students</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -4410,6 +5211,16 @@
           <t>Listed under the Ministry as "Central Sector Scheme of National Fellowship for Providing Fellowship to Scheduled Caste Students to Pursue M.Phil. &amp; PhD" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled Castes · Students</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -4460,6 +5271,16 @@
           <t>Listed under the Ministry as "National Overseas Scholarship For Scheduled Caste Etc. Candidates" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled Castes · De-notified, Nomadic and Semi-Nomadic Tribes · Students</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -4510,6 +5331,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>Safai Karamcharis</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -4560,6 +5391,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled Castes</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -4610,6 +5451,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>Senior Citizens</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>Care, Shelter and Health</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -4660,6 +5511,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>Housing and Settlement</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -4710,6 +5571,16 @@
           <t>Listed under the Ministry as "Loan based Scheme for Pay and Use Community Toilets" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>Safai Karamcharis</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -4760,6 +5631,16 @@
           <t>Listed as a scheme of Maharashtra — myscheme.gov.in/schemes/pmavssspc — confirms it is a State scheme, not the Department's.</t>
         </is>
       </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes · Students</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>Residential Schools, Hostels and Coaching</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -4810,6 +5691,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>Other Backward Classes</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t>Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -4860,6 +5751,16 @@
           <t>Listed under the Ministry as "Pradhan Mantri Dakshta Aur Kushalta Sampann Hitgrahi (PM-DAKSH)" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled Castes · Other Backward Classes · De-notified, Nomadic and Semi-Nomadic Tribes · Safai Karamcharis</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>Skill Training and Livelihood</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -4875,7 +5776,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/pm-special-training-of-geriatric-care-givers/</t>
         </is>
       </c>
-      <c r="D87" s="12" t="inlineStr">
+      <c r="D87" s="14" t="inlineStr">
         <is>
           <t>Yes — a component of another scheme</t>
         </is>
@@ -4908,6 +5809,16 @@
       <c r="J87" s="6" t="inlineStr">
         <is>
           <t>Listed under the Ministry as "PM-Special Training of Geriatric Caregivers" — agrees with this sheet.</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>Senior Citizens</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
+        <is>
+          <t>Skill Training and Livelihood</t>
         </is>
       </c>
     </row>
@@ -4960,6 +5871,16 @@
           <t>Listed under the Ministry as "PM-YASASVI: Top Class School Education for OBC, EBC and DNT Students" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>Other Backward Classes · De-notified, Nomadic and Semi-Nomadic Tribes · Students</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships · Residential Schools, Hostels and Coaching</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -5010,6 +5931,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>Other Backward Classes · De-notified, Nomadic and Semi-Nomadic Tribes · Students</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships · Residential Schools, Hostels and Coaching</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -5060,6 +5991,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes · Students</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
@@ -5110,6 +6051,16 @@
           <t>Listed under the Ministry as "Centrally Sponsored Scheme of Post-Matric Scholarship for OBC Students for studying in India" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled Castes · Students</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -5160,6 +6111,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
@@ -5210,6 +6171,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="L93" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
@@ -5260,6 +6231,16 @@
           <t>Listed under the Ministry as "Pradhan Mantri Anusuchit Jaati Abhyuday Yojana (PM-AJAY) - Adarsh Gram" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled Castes</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>Skill Training and Livelihood · Residential Schools, Hostels and Coaching · Housing and Settlement</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
@@ -5310,6 +6291,16 @@
           <t>Listed under the Ministry as "Pre- Matric Scholarships Scheme for Scheduled Castes &amp; Others" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled Castes · Safai Karamcharis · Students</t>
+        </is>
+      </c>
+      <c r="L95" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -5360,6 +6351,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
@@ -5410,6 +6411,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published on myScheme under a State.</t>
         </is>
       </c>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes · Students</t>
+        </is>
+      </c>
+      <c r="L97" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -5460,6 +6471,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K98" s="13" t="inlineStr">
+        <is>
+          <t>— none (not citizen-facing)</t>
+        </is>
+      </c>
+      <c r="L98" s="13" t="inlineStr">
+        <is>
+          <t>— none (not a benefit)</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
@@ -5510,6 +6531,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>Housing and Settlement</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -5560,6 +6591,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes · Other Backward Classes · Students</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
@@ -5575,7 +6616,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/rashtriya-vayoshri-yojana-rvy/</t>
         </is>
       </c>
-      <c r="D101" s="12" t="inlineStr">
+      <c r="D101" s="14" t="inlineStr">
         <is>
           <t>Yes — a component of another scheme</t>
         </is>
@@ -5608,6 +6649,16 @@
       <c r="J101" s="8" t="inlineStr">
         <is>
           <t>Not on myScheme in any form.</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>Senior Citizens</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>Care, Shelter and Health</t>
         </is>
       </c>
     </row>
@@ -5660,6 +6711,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>Safai Karamcharis</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>Care, Shelter and Health · Skill Training and Livelihood · Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
@@ -5710,6 +6771,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>Safai Karamcharis</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>Care, Shelter and Health · Skill Training and Livelihood · Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -5760,6 +6831,16 @@
           <t>Listed under the Ministry as "Loan Based Schemes For Safai Karamchari - Sanitary Marts Scheme" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>Safai Karamcharis</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
@@ -5810,6 +6891,16 @@
           <t>Listed as a scheme of Maharashtra — myscheme.gov.in/schemes/spsvsgs says "resident of the state of Maharashtra", applied on mahadbt.maharashtra.gov.in — confirms it is a State scheme, not the Department's.</t>
         </is>
       </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes · Students</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -5860,6 +6951,16 @@
           <t>Listed under the Ministry as "Education Loan Scheme" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled Castes · Students · Voluntary Organisations</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>Residential Schools, Hostels and Coaching · Grants to Voluntary Organisations</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
@@ -5910,6 +7011,16 @@
           <t>Listed under the Ministry as "Scheme of Assistance to State Scheduled Castes Development Corporations" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled Castes</t>
+        </is>
+      </c>
+      <c r="L107" s="3" t="inlineStr">
+        <is>
+          <t>Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -5960,6 +7071,16 @@
           <t>Listed under the Ministry as "Scheme of Assistance for the Prevention of Alcoholism &amp; Substance (Drugs) Abuse and for Social Defence Services: General Grant-in-Aid Programme" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t>Persons Affected by Substance Use · Voluntary Organisations</t>
+        </is>
+      </c>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t>Awards and Recognition · De-addiction and Counselling</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
@@ -6010,6 +7131,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K109" s="3" t="inlineStr">
+        <is>
+          <t>Safai Karamcharis</t>
+        </is>
+      </c>
+      <c r="L109" s="3" t="inlineStr">
+        <is>
+          <t>Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -6060,6 +7191,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="L110" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
@@ -6110,6 +7251,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="L111" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -6125,7 +7276,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/scholarships-for-higher-education-for-young-achievers-scheme-shreyas-obc-others-2021-22-to-2025-26/</t>
         </is>
       </c>
-      <c r="D112" s="12" t="inlineStr">
+      <c r="D112" s="14" t="inlineStr">
         <is>
           <t>Yes — a component of another scheme</t>
         </is>
@@ -6158,6 +7309,16 @@
       <c r="J112" s="6" t="inlineStr">
         <is>
           <t>Listed under the Ministry as "Education Loan Scheme" — agrees with this sheet.</t>
+        </is>
+      </c>
+      <c r="K112" s="3" t="inlineStr">
+        <is>
+          <t>Other Backward Classes · Students</t>
+        </is>
+      </c>
+      <c r="L112" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
         </is>
       </c>
     </row>
@@ -6210,6 +7371,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="L113" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -6260,6 +7431,16 @@
           <t>Listed under the Ministry as "Free Coaching Scheme" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes · Students</t>
+        </is>
+      </c>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>Residential Schools, Hostels and Coaching</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
@@ -6275,7 +7456,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/seed-health-insurance/</t>
         </is>
       </c>
-      <c r="D115" s="12" t="inlineStr">
+      <c r="D115" s="14" t="inlineStr">
         <is>
           <t>Yes — a component of another scheme</t>
         </is>
@@ -6308,6 +7489,16 @@
       <c r="J115" s="8" t="inlineStr">
         <is>
           <t>Not on myScheme in any form.</t>
+        </is>
+      </c>
+      <c r="K115" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes</t>
+        </is>
+      </c>
+      <c r="L115" s="3" t="inlineStr">
+        <is>
+          <t>Care, Shelter and Health</t>
         </is>
       </c>
     </row>
@@ -6325,7 +7516,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/seed-housing/</t>
         </is>
       </c>
-      <c r="D116" s="12" t="inlineStr">
+      <c r="D116" s="14" t="inlineStr">
         <is>
           <t>Yes — a component of another scheme</t>
         </is>
@@ -6358,6 +7549,16 @@
       <c r="J116" s="8" t="inlineStr">
         <is>
           <t>Not on myScheme in any form.</t>
+        </is>
+      </c>
+      <c r="K116" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes</t>
+        </is>
+      </c>
+      <c r="L116" s="3" t="inlineStr">
+        <is>
+          <t>Housing and Settlement</t>
         </is>
       </c>
     </row>
@@ -6375,7 +7576,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/seed-livelihood/</t>
         </is>
       </c>
-      <c r="D117" s="12" t="inlineStr">
+      <c r="D117" s="14" t="inlineStr">
         <is>
           <t>Yes — a component of another scheme</t>
         </is>
@@ -6408,6 +7609,16 @@
       <c r="J117" s="8" t="inlineStr">
         <is>
           <t>Not on myScheme in any form.</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes</t>
+        </is>
+      </c>
+      <c r="L117" s="3" t="inlineStr">
+        <is>
+          <t>Skill Training and Livelihood</t>
         </is>
       </c>
     </row>
@@ -6460,6 +7671,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K118" s="3" t="inlineStr">
+        <is>
+          <t>Safai Karamcharis</t>
+        </is>
+      </c>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t>Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
@@ -6510,6 +7731,16 @@
           <t>Listed under the Ministry as "Self Employment Scheme For Rehabilitation Of Manual Scavengers" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K119" s="3" t="inlineStr">
+        <is>
+          <t>Safai Karamcharis</t>
+        </is>
+      </c>
+      <c r="L119" s="3" t="inlineStr">
+        <is>
+          <t>Skill Training and Livelihood · Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -6525,7 +7756,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/seniorcare-ageing-growth-engine-sage/</t>
         </is>
       </c>
-      <c r="D120" s="12" t="inlineStr">
+      <c r="D120" s="14" t="inlineStr">
         <is>
           <t>Yes — a component of another scheme</t>
         </is>
@@ -6558,6 +7789,16 @@
       <c r="J120" s="8" t="inlineStr">
         <is>
           <t>Not on myScheme in any form.</t>
+        </is>
+      </c>
+      <c r="K120" s="3" t="inlineStr">
+        <is>
+          <t>Senior Citizens</t>
+        </is>
+      </c>
+      <c r="L120" s="3" t="inlineStr">
+        <is>
+          <t>Care, Shelter and Health</t>
         </is>
       </c>
     </row>
@@ -6610,6 +7851,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
+          <t>Safai Karamcharis</t>
+        </is>
+      </c>
+      <c r="L121" s="3" t="inlineStr">
+        <is>
+          <t>Skill Training and Livelihood</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
@@ -6660,6 +7911,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K122" s="3" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="L122" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
@@ -6675,7 +7936,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/state-action-plan-for-senior-citizens-sapsrc/</t>
         </is>
       </c>
-      <c r="D123" s="12" t="inlineStr">
+      <c r="D123" s="14" t="inlineStr">
         <is>
           <t>Yes — a component of another scheme</t>
         </is>
@@ -6708,6 +7969,16 @@
       <c r="J123" s="8" t="inlineStr">
         <is>
           <t>Not on myScheme in any form.</t>
+        </is>
+      </c>
+      <c r="K123" s="3" t="inlineStr">
+        <is>
+          <t>Senior Citizens</t>
+        </is>
+      </c>
+      <c r="L123" s="3" t="inlineStr">
+        <is>
+          <t>Care, Shelter and Health</t>
         </is>
       </c>
     </row>
@@ -6760,6 +8031,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K124" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes · Students</t>
+        </is>
+      </c>
+      <c r="L124" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
@@ -6810,6 +8091,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K125" s="3" t="inlineStr">
+        <is>
+          <t>Safai Karamcharis</t>
+        </is>
+      </c>
+      <c r="L125" s="3" t="inlineStr">
+        <is>
+          <t>Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
@@ -6860,6 +8151,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K126" s="3" t="inlineStr">
+        <is>
+          <t>Safai Karamcharis</t>
+        </is>
+      </c>
+      <c r="L126" s="3" t="inlineStr">
+        <is>
+          <t>Skill Training and Livelihood · Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
@@ -6910,6 +8211,16 @@
           <t>Listed under the Ministry as "Support for Marginalized Individuals for Livelihood and Enterprise (SMILE): Composite Medical Health for Transgender Persons" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K127" s="3" t="inlineStr">
+        <is>
+          <t>Transgender Persons · Persons Engaged in Begging · Voluntary Organisations</t>
+        </is>
+      </c>
+      <c r="L127" s="3" t="inlineStr">
+        <is>
+          <t>Care, Shelter and Health · Skill Training and Livelihood · Protection, Relief and Grievance · Grants to Voluntary Organisations</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
@@ -6960,6 +8271,16 @@
           <t>Listed under the Ministry as "Loan Based Schemes For Safai Karamchari - Swachhta Udyami Yojana" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K128" s="3" t="inlineStr">
+        <is>
+          <t>Safai Karamcharis</t>
+        </is>
+      </c>
+      <c r="L128" s="3" t="inlineStr">
+        <is>
+          <t>Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
@@ -7010,6 +8331,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K129" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes · Students</t>
+        </is>
+      </c>
+      <c r="L129" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
@@ -7060,6 +8391,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K130" s="3" t="inlineStr">
+        <is>
+          <t>Other Backward Classes</t>
+        </is>
+      </c>
+      <c r="L130" s="3" t="inlineStr">
+        <is>
+          <t>Skill Training and Livelihood</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
@@ -7075,7 +8416,7 @@
           <t>https://www.dosje.gov.in/schemes-and-services/top-class-education-in-colllege-for-obc-ebc-and-dnt-students/</t>
         </is>
       </c>
-      <c r="D131" s="12" t="inlineStr">
+      <c r="D131" s="14" t="inlineStr">
         <is>
           <t>Yes — a component of another scheme</t>
         </is>
@@ -7108,6 +8449,16 @@
       <c r="J131" s="6" t="inlineStr">
         <is>
           <t>Listed under the Ministry as "Education Loan Scheme" — agrees with this sheet.</t>
+        </is>
+      </c>
+      <c r="K131" s="3" t="inlineStr">
+        <is>
+          <t>Other Backward Classes · De-notified, Nomadic and Semi-Nomadic Tribes · Students</t>
+        </is>
+      </c>
+      <c r="L131" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
         </is>
       </c>
     </row>
@@ -7160,6 +8511,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K132" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes · Other Backward Classes</t>
+        </is>
+      </c>
+      <c r="L132" s="3" t="inlineStr">
+        <is>
+          <t>Skill Training and Livelihood</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
@@ -7210,6 +8571,16 @@
           <t>Listed as a scheme of Maharashtra — myscheme.gov.in/schemes/tfefvssshs — confirms it is a State scheme, not the Department's.</t>
         </is>
       </c>
+      <c r="K133" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes · Students</t>
+        </is>
+      </c>
+      <c r="L133" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
@@ -7260,6 +8631,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K134" s="3" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="L134" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
@@ -7310,6 +8691,16 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K135" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled Castes</t>
+        </is>
+      </c>
+      <c r="L135" s="3" t="inlineStr">
+        <is>
+          <t>Loans and Credit</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
@@ -7360,6 +8751,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K136" s="3" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="L136" s="3" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
@@ -7410,6 +8811,16 @@
           <t>Listed under the Ministry as "Centrally Sponsored Scheme of Upgradation of Merit of Scheduled Caste Students" — agrees with this sheet.</t>
         </is>
       </c>
+      <c r="K137" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled Castes · Students</t>
+        </is>
+      </c>
+      <c r="L137" s="3" t="inlineStr">
+        <is>
+          <t>Residential Schools, Hostels and Coaching</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
@@ -7460,6 +8871,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K138" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes</t>
+        </is>
+      </c>
+      <c r="L138" s="3" t="inlineStr">
+        <is>
+          <t>Housing and Settlement</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
@@ -7510,6 +8931,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K139" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes · Students</t>
+        </is>
+      </c>
+      <c r="L139" s="3" t="inlineStr">
+        <is>
+          <t>Residential Schools, Hostels and Coaching</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
@@ -7560,6 +8991,16 @@
           <t>Not among myScheme's 85 Ministry schemes. Nine schemes of this set were checked individually and every one is published under a State.</t>
         </is>
       </c>
+      <c r="K140" s="3" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes · Students</t>
+        </is>
+      </c>
+      <c r="L140" s="3" t="inlineStr">
+        <is>
+          <t>Skill Training and Livelihood</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
@@ -7610,9 +9051,19 @@
           <t>Not on myScheme in any form.</t>
         </is>
       </c>
+      <c r="K141" s="3" t="inlineStr">
+        <is>
+          <t>Safai Karamcharis</t>
+        </is>
+      </c>
+      <c r="L141" s="3" t="inlineStr">
+        <is>
+          <t>Skill Training and Livelihood</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J141"/>
+  <autoFilter ref="A1:L141"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -7774,243 +9225,243 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>What is listed under Schemes &amp; Services on dosje.gov.in, read on 9 September 2026</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Verdict</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Records</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>What it means</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="B4" s="15" t="n">
+      <c r="B4" s="17" t="n">
         <v>31</v>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>A scheme of this Department in its own right</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Yes — a component of another scheme</t>
         </is>
       </c>
-      <c r="B5" s="15" t="n">
+      <c r="B5" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>Real, but it belongs inside its umbrella (PM-YASASVI, SEED, AVYAY), not beside it</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>Yes — but already listed under another name</t>
         </is>
       </c>
-      <c r="B6" s="15" t="n">
+      <c r="B6" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>The same scheme published twice</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>To confirm</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n">
+      <c r="B7" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>Could not be settled from the Department's own published sources</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B8" s="15" t="n">
+      <c r="B8" s="17" t="n">
         <v>86</v>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>Not a scheme of this Department at all</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="18" t="n">
         <v>140</v>
       </c>
-      <c r="C9" s="16" t="inlineStr"/>
+      <c r="C9" s="18" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Of the 86 that are not schemes</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>Records</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>Where they go</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>A State Government scheme</t>
         </is>
       </c>
-      <c r="B13" s="15" t="n">
+      <c r="B13" s="17" t="n">
         <v>46</v>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>A labelled State-schemes directory under DWBDNC, every entry naming its State</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>A corporation 's loan product or activity</t>
         </is>
       </c>
-      <c r="B14" s="15" t="n">
+      <c r="B14" s="17" t="n">
         <v>21</v>
       </c>
-      <c r="C14" s="15" t="inlineStr"/>
+      <c r="C14" s="17" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>A document</t>
         </is>
       </c>
-      <c r="B15" s="15" t="n">
+      <c r="B15" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>Documents — Acts, Rules &amp; Guidelines, and Publications</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>A status or achievement table</t>
         </is>
       </c>
-      <c r="B16" s="15" t="n">
+      <c r="B16" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>Dashboard / Statistics, or RTI suo-moto disclosure</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>An organisation or institution</t>
         </is>
       </c>
-      <c r="B17" s="15" t="n">
+      <c r="B17" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>Organisation pages, all four of which already exist on this site</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>A duplicate listing</t>
         </is>
       </c>
-      <c r="B18" s="15" t="n">
+      <c r="B18" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>Delete, with a redirect</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>A reference list</t>
         </is>
       </c>
-      <c r="B19" s="15" t="n">
+      <c r="B19" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>Acts &amp; Rules, as an annexe to the PoA Act 1989</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>A memorandum of understanding</t>
         </is>
       </c>
-      <c r="B20" s="15" t="n">
+      <c r="B20" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>Documents — MoU</t>
         </is>
@@ -8022,6 +9473,1068 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>Every record tagged against the eleven personas and the ten categories</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>Columns K and L of the first tab carry these tags. A record can hold several of each, so the counts below do not sum to 140. Housing and Settlement and Awards and Recognition were added to the model on 11 September 2026 and are now part of it — the scheme master, the prototype data, the app and the deck all carry them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Who Is Looking for Support</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>All 140 records</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>The 48 that are the Department's</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n">
+        <v>59</v>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>Scheduled Castes</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>Other Backward Classes</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>Safai Karamcharis</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>Senior Citizens</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>Transgender Persons</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>Persons Affected by Substance Use</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>Persons Engaged in Begging</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>Victims of Atrocities</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>Voluntary Organisations</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>What the Department Provides</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>All 140 records</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>The 48 that are the Department's</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>Scholarships and Fellowships</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>Residential Schools, Hostels and Coaching</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="C20" s="17" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>Loans and Credit</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="C21" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>Skill Training and Livelihood</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="C22" s="17" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>Care, Shelter and Health</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="C23" s="17" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>De-addiction and Counselling</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>Protection, Relief and Grievance</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C25" s="17" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>Grants to Voluntary Organisations</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="C26" s="17" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>Housing and Settlement</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="C27" s="18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>Awards and Recognition</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="C28" s="18" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>The two categories added on 11 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>Housing and Settlement</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>Eleven records describe a house, a plot, a basti, roads or drainage: CM Housing Rent, Gadia Lohar, Housing Plan, Housing Scheme for SCs and DNTs, Infrastructure for NT/SNT, Pandit Din Dayal Upadhyay Awas Yojana, Purchase of Land for the Homeless, SEED — Housing, Vimukt Jaati Basti Development, Basti Development, and PM-AJAY's Adarsh Gram component. The master had filed Adarsh Gram under Skill Training and Livelihood, which is a reading nobody would make.</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>Awards and Recognition</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>Ten records are a prize, a merit award, a chair or a national award, not assistance anybody applies for: both Dr. Ambedkar National Merit Awards, the DAF and BJR essay competitions, the BJR and Dr. Ambedkar Chairs, District Level Prizes, the Civil Service Incentive, the Excellent Award for Social Workers, and the National Awards for prevention of alcoholism. Filing a prize under Scholarships and Fellowships makes a student expect money for studying.</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>Where Housing and Settlement stops and Care, Shelter and Health begins</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>A shelter home, a Garima Greh, an old-age home and a de-addiction centre stay under Care, Shelter and Health — the citizen is housed there for a time, by somebody else. Housing and Settlement is a permanent home the citizen holds, or the works of the settlement they live in. Without this line the two categories will blur within a month.</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>Three records carry no persona and no category</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>Dr. Ambedkar International Centre · Dr. Ambedkar National Memorial · Publication of the Collected Works of Babasaheb</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>None is a benefit to a person. Two are places and one is a publication programme — the clearest proof that the list holds things the tagging model was never meant to describe.</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="17" t="inlineStr">
+        <is>
+          <t>Dr. Ambedkar Chairs · Babu Jagjivan Ram Chair Scheme</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>These now have a category (Awards and Recognition) but still no citizen persona — the beneficiary is a university. Either the personas gain a twelfth entry for institutions, or these move to a Research and Commemoration section.</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>The 48 Department records, counted by persona and category</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>A number is how many records serve that persona AND provide that category. A blank cell is a gap — the Department publishes nothing there, so the finder must be written to say so rather than return an empty result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr"/>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>Scholarships</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>Schools &amp; Coaching</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>Loans</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>Skill &amp; Livelihood</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>Care &amp; Health</t>
+        </is>
+      </c>
+      <c r="G5" s="16" t="inlineStr">
+        <is>
+          <t>De-addiction</t>
+        </is>
+      </c>
+      <c r="H5" s="16" t="inlineStr">
+        <is>
+          <t>Protection</t>
+        </is>
+      </c>
+      <c r="I5" s="16" t="inlineStr">
+        <is>
+          <t>Grants to VOs</t>
+        </is>
+      </c>
+      <c r="J5" s="16" t="inlineStr">
+        <is>
+          <t>Housing</t>
+        </is>
+      </c>
+      <c r="K5" s="16" t="inlineStr">
+        <is>
+          <t>Awards</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="C6" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" s="23" t="inlineStr"/>
+      <c r="E6" s="23" t="inlineStr"/>
+      <c r="F6" s="23" t="inlineStr"/>
+      <c r="G6" s="23" t="inlineStr"/>
+      <c r="H6" s="23" t="inlineStr"/>
+      <c r="I6" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="23" t="inlineStr"/>
+      <c r="K6" s="22" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>Scheduled Castes</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="23" t="inlineStr"/>
+      <c r="E7" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="23" t="inlineStr"/>
+      <c r="H7" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>Other Backward Classes</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" s="23" t="inlineStr"/>
+      <c r="E8" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="23" t="inlineStr"/>
+      <c r="G8" s="23" t="inlineStr"/>
+      <c r="H8" s="23" t="inlineStr"/>
+      <c r="I8" s="23" t="inlineStr"/>
+      <c r="J8" s="23" t="inlineStr"/>
+      <c r="K8" s="23" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>De-notified, Nomadic and Semi-Nomadic Tribes</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="23" t="inlineStr"/>
+      <c r="E9" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="23" t="inlineStr"/>
+      <c r="H9" s="23" t="inlineStr"/>
+      <c r="I9" s="23" t="inlineStr"/>
+      <c r="J9" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="23" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>Safai Karamcharis</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="23" t="inlineStr"/>
+      <c r="D10" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="23" t="inlineStr"/>
+      <c r="H10" s="23" t="inlineStr"/>
+      <c r="I10" s="23" t="inlineStr"/>
+      <c r="J10" s="23" t="inlineStr"/>
+      <c r="K10" s="23" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>Senior Citizens</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr"/>
+      <c r="C11" s="23" t="inlineStr"/>
+      <c r="D11" s="23" t="inlineStr"/>
+      <c r="E11" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" s="23" t="inlineStr"/>
+      <c r="H11" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" s="23" t="inlineStr"/>
+      <c r="K11" s="23" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>Transgender Persons</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr"/>
+      <c r="C12" s="23" t="inlineStr"/>
+      <c r="D12" s="23" t="inlineStr"/>
+      <c r="E12" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="23" t="inlineStr"/>
+      <c r="H12" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="23" t="inlineStr"/>
+      <c r="K12" s="23" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>Persons Affected by Substance Use</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr"/>
+      <c r="C13" s="23" t="inlineStr"/>
+      <c r="D13" s="23" t="inlineStr"/>
+      <c r="E13" s="23" t="inlineStr"/>
+      <c r="F13" s="23" t="inlineStr"/>
+      <c r="G13" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" s="23" t="inlineStr"/>
+      <c r="I13" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="23" t="inlineStr"/>
+      <c r="K13" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>Persons Engaged in Begging</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr"/>
+      <c r="C14" s="23" t="inlineStr"/>
+      <c r="D14" s="23" t="inlineStr"/>
+      <c r="E14" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="23" t="inlineStr"/>
+      <c r="H14" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="23" t="inlineStr"/>
+      <c r="K14" s="23" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>Victims of Atrocities</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr"/>
+      <c r="C15" s="23" t="inlineStr"/>
+      <c r="D15" s="23" t="inlineStr"/>
+      <c r="E15" s="23" t="inlineStr"/>
+      <c r="F15" s="23" t="inlineStr"/>
+      <c r="G15" s="23" t="inlineStr"/>
+      <c r="H15" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" s="23" t="inlineStr"/>
+      <c r="J15" s="23" t="inlineStr"/>
+      <c r="K15" s="23" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>Voluntary Organisations</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr"/>
+      <c r="C16" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="23" t="inlineStr"/>
+      <c r="E16" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="J16" s="23" t="inlineStr"/>
+      <c r="K16" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>63 of the 110 cells are empty. Transgender Persons, Persons Engaged in Begging and Persons Affected by Substance Use are each served by one or two records — every other cell on those rows is blank.</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="17" t="n"/>
+      <c r="G18" s="17" t="n"/>
+      <c r="H18" s="17" t="n"/>
+      <c r="I18" s="17" t="n"/>
+      <c r="J18" s="17" t="n"/>
+      <c r="K18" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="86" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>Filters the two lists cannot provide on their own</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>Why it earns a place</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>Can the data support it today?</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>Who runs it</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Union Government · State Government · the Department's corporations</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>The single most-needed filter, and the defect this audit found: 46 State schemes sit beside 20 Union schemes with nothing to tell them apart. A reader cannot tell which government they are applying to.</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>Yes — column F of the first tab already carries it for all 140.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>Open · Applications closed · Merged into another scheme · Closed</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>Four records are merged or closed and look exactly as live as Post-Matric Scholarship. Without this, the list quietly misleads.</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>Partly — the four are identified; the rest need the Department to confirm each window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>Stage of education</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>Class I–VIII · Class IX–X · Class XI–XII · Graduation · Post-graduation · PhD · Study abroad</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>Sixty of the 140 records are education, and 'Students' as one persona is far too coarse — a Class VI pupil and a PhD candidate get the same result set.</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>Yes — 60 records already name a stage in their own text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>Income ceiling</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>No income limit · up to Rs 1 lakh · up to Rs 2.5 lakh · up to Rs 3 lakh · up to Rs 8 lakh</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>The first thing that disqualifies an applicant, and the first thing they want to check.</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Not yet — only 21 of 140 records state a figure. The Department would have to supply the rest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>Who can apply</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>A person · a family · a self-help group · an NGO or institution · a State or district government</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Several entries can only be applied for by a government or an NGO — PM-AJAY, Assistance to SCDCs, the grant-in-aid schemes. A citizen filtering by persona gets them today with no way to know they cannot apply.</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>Yes — derivable from the records, and already implied by the Voluntary Organisations persona.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>Where you apply</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>National Scholarship Portal · the State's portal · a corporation · e-Anudaan · a helpline · the district administration</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>This is the 'Services' half of the section's own name, which has never had anything behind it.</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>Yes — the scheme master already records an application route for each of its 38 schemes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>What you receive</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>Money · fees waived · equipment or goods · a place to live · training · a loan · legal or grievance help</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>myScheme publishes a national version of this (Cash / In Kind / Composite), so a citizen has met the idea before.</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>Yes, with a pass over the records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>Two filters we recommend against</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>The scheme master deliberately kept gender out of the personas: it is a reservation inside schemes — 30% of Top Class slots, 50% of the overseas subsidy, the NSKFDC women's loan schemes — not a target group. As a filter it would return four or five schemes and imply every other scheme excludes women.</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>Only add if the Department asks for it.</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>Disability</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>Outside this Department's mandate. Those schemes belong to the Department of Empowerment of Persons with Disabilities, a separate Department of the same Ministry since 2012 — and myScheme's own Ministry page mixes twenty of them in, which is exactly the confusion to avoid.</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>Do not add.</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8035,268 +10548,268 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Checked against myScheme.gov.in, the National Government scheme portal, 9 September 2026</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>myScheme's ministry page lists 85 schemes under "Ministry Of Social Justice and Empowerment". Twenty of those are schemes of the Department of Empowerment of Persons with Disabilities, the other Department of the same Ministry — leaving 65 that belong to this Department and its corporations. That is the set this sheet was checked against.</t>
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>myScheme's ministry page lists 85 schemes under "Ministry Of Social Justice and Empowerment". Twenty are schemes of the Department of Empowerment of Persons with Disabilities, the other Department of the same Ministry — leaving 65 that belong to this Department and its corporations. That is the set this sheet was checked against.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>Records</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr"/>
+      <c r="C5" s="16" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>Listed on myScheme under the Ministry — agrees with this sheet</t>
         </is>
       </c>
-      <c r="B6" s="15" t="n">
+      <c r="B6" s="17" t="n">
         <v>40</v>
       </c>
-      <c r="C6" s="15" t="inlineStr"/>
+      <c r="C6" s="17" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Listed on myScheme under a State Government — confirms it is not the Department's</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n">
+      <c r="B7" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="C7" s="15" t="inlineStr"/>
+      <c r="C7" s="17" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Not on myScheme in any form</t>
         </is>
       </c>
-      <c r="B8" s="15" t="n">
+      <c r="B8" s="17" t="n">
         <v>91</v>
       </c>
-      <c r="C8" s="15" t="inlineStr"/>
+      <c r="C8" s="17" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>Where myScheme and this sheet disagree</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>Ten records. Every one is a corporation loan product — Term Loan, Education Loan, GTL, Green Business, NBCFDC General Loan, Mahila Samriddhi, Micro Credit Finance, Pay &amp; Use Toilets, Sanitary Marts, Swachhta Udyami. myScheme publishes them as schemes of the Ministry; this sheet says they are products of the Department's corporations rather than schemes of the Department's own budget. Both are true. The disagreement is about the word "scheme", not about the facts: none of the ten carries a line in Demand No. 93, and all ten are administered by NSFDC, NSKFDC or NBCFDC. The placement recommendation is unchanged — they belong together under the corporations — but they should not be described to a citizen as though they were not schemes.</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="15" t="n"/>
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>Ten records, every one a corporation loan product — Term Loan, Education Loan, GTL, Green Business, NBCFDC General Loan, Mahila Samriddhi, Micro Credit Finance, Pay &amp; Use Toilets, Sanitary Marts, Swachhta Udyami. myScheme publishes them as schemes of the Ministry; this sheet says they are products of the Department's corporations rather than schemes of its own budget. Both are true. None carries a line in Demand No. 93, and all ten are administered by NSFDC, NSKFDC or NBCFDC. The placement recommendation is unchanged, but they should not be described to a citizen as though they were not schemes.</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>What myScheme settles that our own sources could not</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>Credit Enhancement Guarantee Scheme for the Scheduled Castes</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>Published on myScheme under the Ministry. Treat as live, subject to the Department's confirmation.</t>
         </is>
       </c>
-      <c r="C14" s="15" t="n"/>
+      <c r="C14" s="17" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>Scheme of Assistance to SC Development Corporations</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>Published on myScheme as "Scheme of Assistance to State Scheduled Castes Development Corporations". Treat as live.</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="n"/>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>Published as 'Scheme of Assistance to State Scheduled Castes Development Corporations'. Treat as live.</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>Upgradation of Merit of SC Students</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>Published on myScheme as a Centrally Sponsored Scheme. Treat as live.</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="n"/>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>Published as a Centrally Sponsored Scheme. Treat as live.</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>Self Employment Scheme for Rehabilitation of Manual Scavengers (SRMS)</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>Still published on myScheme, although the Annual Report 2025-26 §3.11 records it as subsumed into NAMASTE from 2023-24. The two sources conflict; the Annual Report is the Department's own and should win.</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="n"/>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>Still published on myScheme, although Annual Report 2025-26 §3.11 records it subsumed into NAMASTE from 2023-24. The Annual Report is the Department's own and should win.</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>What myScheme lists that our Schemes page does not carry at all</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>These are schemes of this Department, published on the National portal, and absent from the site's own list of 140 — while 86 things that are not the Department's schemes are on it.</t>
         </is>
       </c>
-      <c r="B20" s="15" t="n"/>
-      <c r="C20" s="15" t="n"/>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>VISVAS Yojana — interest subvention, for individuals and for self-help groups (Annual Report §3.25, Demand No. 93 line 10)</t>
         </is>
       </c>
-      <c r="B21" s="15" t="n"/>
-      <c r="C21" s="15" t="n"/>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>Venture Capital Fund for Scheduled Castes, and Ambedkar Social Innovation and Incubation Mission (ASIIM) (Annual Report §3.12, line 12)</t>
         </is>
       </c>
-      <c r="B22" s="15" t="n"/>
-      <c r="C22" s="15" t="n"/>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="17" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>Garima Greh — shelter homes for transgender persons, and SMILE's transgender sub-scheme as an entry of its own</t>
         </is>
       </c>
-      <c r="B23" s="15" t="n"/>
-      <c r="C23" s="15" t="n"/>
+      <c r="B23" s="17" t="n"/>
+      <c r="C23" s="17" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>Scheme for Supportive Money to the Parents of Transgender Children</t>
         </is>
       </c>
-      <c r="B24" s="15" t="n"/>
-      <c r="C24" s="15" t="n"/>
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="17" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>Scheme of Grant-in-Aid to Voluntary and other Organizations Working for Scheduled Castes</t>
         </is>
       </c>
-      <c r="B25" s="15" t="n"/>
-      <c r="C25" s="15" t="n"/>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>Assistance to Voluntary Organizations Working for Welfare of OBCs</t>
         </is>
       </c>
-      <c r="B26" s="15" t="n"/>
-      <c r="C26" s="15" t="n"/>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>Centrally Sponsored Pre-matric and Post-Matric Scholarships for OBC students, and the Dr. Ambedkar Post-Matric Scholarship for EBC students, as entries of their own</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n"/>
-      <c r="C27" s="15" t="n"/>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="17" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>I-MESA — Information, Monitoring, Evaluation and Social Audit, in four components</t>
         </is>
       </c>
-      <c r="B28" s="15" t="n"/>
-      <c r="C28" s="15" t="n"/>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>Rashtriya Parivar Sahayata Yojana</t>
         </is>
       </c>
-      <c r="B29" s="15" t="n"/>
-      <c r="C29" s="15" t="n"/>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>New Swarnima Scheme for Women, Vocational Education and Training Loan Scheme, and the NSFDC Internship Scheme</t>
         </is>
       </c>
-      <c r="B30" s="15" t="n"/>
-      <c r="C30" s="15" t="n"/>
+      <c r="B30" s="17" t="n"/>
+      <c r="C30" s="17" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>What our sources carry that myScheme does not</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>myScheme lists none of the Dr. Ambedkar Foundation or Babu Jagjivan Ram National Foundation schemes, and none of AVYAY's senior-citizen components individually — no Elderline, no Integrated Programme for Senior Citizens, no Rashtriya Vayoshri Yojana as its own entry, no SAGE. Nor the National Action Plan for Drug Demand Reduction. Absence from myScheme is therefore not evidence that a scheme does not exist; it is evidence that the National portal's coverage of this Department is incomplete.</t>
         </is>
       </c>
-      <c r="B33" s="15" t="n"/>
-      <c r="C33" s="15" t="n"/>
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="17" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8311,1299 +10824,1299 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Every scheme myScheme publishes under "Ministry Of Social Justice and Empowerment", captured 9 September 2026</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Scheme name on myScheme</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>Whose it is</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="n">
+      <c r="A4" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Persons With Disabilities Scheme In Colleges: Higher Education For Persons With Special Needs</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>Dept. of Empowerment of Persons with Disabilities</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n">
+      <c r="A5" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>Centrally Sponsored Scheme of Pre-matric Scholarship to Other Backward Classes (OBC) for Studies in India</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n">
+      <c r="A6" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>Green Business Scheme</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="n">
+      <c r="A7" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>The NSFDC Internship Scheme</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Venture Capital Fund for Scheduled Castes</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="n">
+      <c r="A9" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>Dr Ambedkar Central Sector Scheme of Interest Subsidy on Educational Loans for Overseas Studies for Other Backward Classes (OBCs) and Economically Backward Classes (EBCs)</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n">
+      <c r="A10" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Pre-Matric Scholarship for Scheduled Caste Students</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="n">
+      <c r="A11" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Post Matric Scholarship Students With Disabilities</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>Dept. of Empowerment of Persons with Disabilities</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n">
+      <c r="A12" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Top Class Education For Scheduled Caste Students</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n">
+      <c r="A13" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Pre Matric Scholarship For Students With Disabilities</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>Dept. of Empowerment of Persons with Disabilities</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="n">
+      <c r="A14" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>Vanchit Ikai Samooh aur Vargon ki Aarthik Sahayata Yojana (VISVAS) for Individual</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="n">
+      <c r="A15" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>NBCFDC General Loan Scheme</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="n">
+      <c r="A16" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>Free Coaching for SCs, OBCs and beneficiaries of PM CARES Children Scheme</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="17" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>PM-YASASVI: Top Class School Education for OBC, EBC and DNT Students</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n">
+      <c r="A18" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>PM-Special Training of Geriatric Caregivers</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="n">
+      <c r="A19" s="17" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>Support for Marginalized Individuals for Livelihood and Enterprise (SMILE): Composite Medical Health for Transgender Persons</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="n">
+      <c r="A20" s="17" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>Information, Monitoring, Evaluation and Social Audit (I-MESA): Project Monitoring Unit (PMU)</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="n">
+      <c r="A21" s="17" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>AVYAY - National Action Plan for Senior Citizens: Health and Shelter for Senior Citizens</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="n">
+      <c r="A22" s="17" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>Information-Monitoring, Evaluation, and Social Audit (I-MESA): Social Audit</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="n">
+      <c r="A23" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>Vikaas-Day Care Scheme For Person with Disability Children</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>Dept. of Empowerment of Persons with Disabilities</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="n">
+      <c r="A24" s="17" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>Top Class Education For Students With Disabilities</t>
         </is>
       </c>
-      <c r="C24" s="15" t="inlineStr">
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>Dept. of Empowerment of Persons with Disabilities</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="n">
+      <c r="A25" s="17" t="n">
         <v>22</v>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>National Overseas Scholarship For Scheduled Caste Etc. Candidates</t>
         </is>
       </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="C25" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="n">
+      <c r="A26" s="17" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>National Overseas Scholarship For Students With Disabilities</t>
         </is>
       </c>
-      <c r="C26" s="15" t="inlineStr">
+      <c r="C26" s="17" t="inlineStr">
         <is>
           <t>Dept. of Empowerment of Persons with Disabilities</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="n">
+      <c r="A27" s="17" t="n">
         <v>24</v>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B27" s="17" t="inlineStr">
         <is>
           <t>Free Coaching for Students with Disabilities</t>
         </is>
       </c>
-      <c r="C27" s="15" t="inlineStr">
+      <c r="C27" s="17" t="inlineStr">
         <is>
           <t>Dept. of Empowerment of Persons with Disabilities</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="n">
+      <c r="A28" s="17" t="n">
         <v>25</v>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>Niramaya Health Insurance Scheme</t>
         </is>
       </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="C28" s="17" t="inlineStr">
         <is>
           <t>Dept. of Empowerment of Persons with Disabilities</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="n">
+      <c r="A29" s="17" t="n">
         <v>26</v>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B29" s="17" t="inlineStr">
         <is>
           <t>Centrally Sponsored Scheme for Implementation of the Protection of Civil Rights Act, 1955 and the Scheduled Castes and the Scheduled Tribes (Prevention of Atrocities) Act, 1989</t>
         </is>
       </c>
-      <c r="C29" s="15" t="inlineStr">
+      <c r="C29" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="n">
+      <c r="A30" s="17" t="n">
         <v>27</v>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>Scheme of Assistance to State Scheduled Castes Development Corporations</t>
         </is>
       </c>
-      <c r="C30" s="15" t="inlineStr">
+      <c r="C30" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="n">
+      <c r="A31" s="17" t="n">
         <v>28</v>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>Ambedkar Social Innovation and Incubation Mission (ASIIM)</t>
         </is>
       </c>
-      <c r="C31" s="15" t="inlineStr">
+      <c r="C31" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="n">
+      <c r="A32" s="17" t="n">
         <v>29</v>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B32" s="17" t="inlineStr">
         <is>
           <t>Disha - Early Intervention and School Readiness Scheme</t>
         </is>
       </c>
-      <c r="C32" s="15" t="inlineStr">
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>Dept. of Empowerment of Persons with Disabilities</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="n">
+      <c r="A33" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B33" s="17" t="inlineStr">
         <is>
           <t>Free Coaching Scheme</t>
         </is>
       </c>
-      <c r="C33" s="15" t="inlineStr">
+      <c r="C33" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="n">
+      <c r="A34" s="17" t="n">
         <v>31</v>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B34" s="17" t="inlineStr">
         <is>
           <t>Pradhan Mantri Dakshta Aur Kushalta Sampann Hitgrahi (PM-DAKSH)</t>
         </is>
       </c>
-      <c r="C34" s="15" t="inlineStr">
+      <c r="C34" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="n">
+      <c r="A35" s="17" t="n">
         <v>32</v>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B35" s="17" t="inlineStr">
         <is>
           <t>Loan Based Schemes For Safai Karamchari - Education Loan</t>
         </is>
       </c>
-      <c r="C35" s="15" t="inlineStr">
+      <c r="C35" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="n">
+      <c r="A36" s="17" t="n">
         <v>33</v>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B36" s="17" t="inlineStr">
         <is>
           <t>Centrally Sponsored Scheme of Post-Matric Scholarship for OBC Students for studying in India</t>
         </is>
       </c>
-      <c r="C36" s="15" t="inlineStr">
+      <c r="C36" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="n">
+      <c r="A37" s="17" t="n">
         <v>34</v>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B37" s="17" t="inlineStr">
         <is>
           <t>Central Sector Scheme of National Fellowship for Providing Fellowship to Scheduled Caste Students to Pursue M.Phil. &amp; PhD</t>
         </is>
       </c>
-      <c r="C37" s="15" t="inlineStr">
+      <c r="C37" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="n">
+      <c r="A38" s="17" t="n">
         <v>35</v>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B38" s="17" t="inlineStr">
         <is>
           <t>Education Loan Scheme</t>
         </is>
       </c>
-      <c r="C38" s="15" t="inlineStr">
+      <c r="C38" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="n">
+      <c r="A39" s="17" t="n">
         <v>36</v>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B39" s="17" t="inlineStr">
         <is>
           <t>PM-YASASVI: Post-Matric Scholarship for OBC, EBC and DNT Students</t>
         </is>
       </c>
-      <c r="C39" s="15" t="inlineStr">
+      <c r="C39" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="n">
+      <c r="A40" s="17" t="n">
         <v>37</v>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B40" s="17" t="inlineStr">
         <is>
           <t>Garima Greh Shelter Homes For Transgender Persons</t>
         </is>
       </c>
-      <c r="C40" s="15" t="inlineStr">
+      <c r="C40" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="n">
+      <c r="A41" s="17" t="n">
         <v>38</v>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B41" s="17" t="inlineStr">
         <is>
           <t>Vocational Education and Training Loan Scheme</t>
         </is>
       </c>
-      <c r="C41" s="15" t="inlineStr">
+      <c r="C41" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="n">
+      <c r="A42" s="17" t="n">
         <v>39</v>
       </c>
-      <c r="B42" s="15" t="inlineStr">
+      <c r="B42" s="17" t="inlineStr">
         <is>
           <t>Post-Matric Scholarship for SC students</t>
         </is>
       </c>
-      <c r="C42" s="15" t="inlineStr">
+      <c r="C42" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="n">
+      <c r="A43" s="17" t="n">
         <v>40</v>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B43" s="17" t="inlineStr">
         <is>
           <t>National Action Plan for Skill Development of Persons with Disabilities</t>
         </is>
       </c>
-      <c r="C43" s="15" t="inlineStr">
+      <c r="C43" s="17" t="inlineStr">
         <is>
           <t>Dept. of Empowerment of Persons with Disabilities</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="n">
+      <c r="A44" s="17" t="n">
         <v>41</v>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B44" s="17" t="inlineStr">
         <is>
           <t>Scheme For Residential Education For Students in High Schools in Targeted Areas (SHRESHTA): Mode 1 - SHRESHTA Schools (Best CBSE Private Residential Schools)</t>
         </is>
       </c>
-      <c r="C44" s="15" t="inlineStr">
+      <c r="C44" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="15" t="n">
+      <c r="A45" s="17" t="n">
         <v>42</v>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B45" s="17" t="inlineStr">
         <is>
           <t>Scheme For Residential Education For Students in High Schools in Targeted Areas (SHRESHTA): Mode 2 - NGO Operated Schools</t>
         </is>
       </c>
-      <c r="C45" s="15" t="inlineStr">
+      <c r="C45" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="n">
+      <c r="A46" s="17" t="n">
         <v>43</v>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B46" s="17" t="inlineStr">
         <is>
           <t>Scholarships for Higher Education for Young Achievers Scheme (SHREYAS)  (OBC &amp; Others)</t>
         </is>
       </c>
-      <c r="C46" s="15" t="inlineStr">
+      <c r="C46" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="n">
+      <c r="A47" s="17" t="n">
         <v>44</v>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B47" s="17" t="inlineStr">
         <is>
           <t>Samarth-Respite Care Scheme</t>
         </is>
       </c>
-      <c r="C47" s="15" t="inlineStr">
+      <c r="C47" s="17" t="inlineStr">
         <is>
           <t>Dept. of Empowerment of Persons with Disabilities</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="n">
+      <c r="A48" s="17" t="n">
         <v>45</v>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B48" s="17" t="inlineStr">
         <is>
           <t>Pre- Matric Scholarships Scheme for Scheduled Castes &amp; Others</t>
         </is>
       </c>
-      <c r="C48" s="15" t="inlineStr">
+      <c r="C48" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="15" t="n">
+      <c r="A49" s="17" t="n">
         <v>46</v>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="B49" s="17" t="inlineStr">
         <is>
           <t>New Swarnima Scheme For Women</t>
         </is>
       </c>
-      <c r="C49" s="15" t="inlineStr">
+      <c r="C49" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="15" t="n">
+      <c r="A50" s="17" t="n">
         <v>47</v>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B50" s="17" t="inlineStr">
         <is>
           <t>Pre-Matric Scholarships to the Children of Those Engaged in Occupations Involving Cleaning and Prone to Health Hazards</t>
         </is>
       </c>
-      <c r="C50" s="15" t="inlineStr">
+      <c r="C50" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="15" t="n">
+      <c r="A51" s="17" t="n">
         <v>48</v>
       </c>
-      <c r="B51" s="15" t="inlineStr">
+      <c r="B51" s="17" t="inlineStr">
         <is>
           <t>National Fellowship for Students with Disabilities</t>
         </is>
       </c>
-      <c r="C51" s="15" t="inlineStr">
+      <c r="C51" s="17" t="inlineStr">
         <is>
           <t>Dept. of Empowerment of Persons with Disabilities</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="15" t="n">
+      <c r="A52" s="17" t="n">
         <v>49</v>
       </c>
-      <c r="B52" s="15" t="inlineStr">
+      <c r="B52" s="17" t="inlineStr">
         <is>
           <t>Mahila Samriddhi Yojana</t>
         </is>
       </c>
-      <c r="C52" s="15" t="inlineStr">
+      <c r="C52" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="15" t="n">
+      <c r="A53" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="B53" s="15" t="inlineStr">
+      <c r="B53" s="17" t="inlineStr">
         <is>
           <t>Centrally Sponsored Scheme of Upgradation of Merit of Scheduled Caste Students</t>
         </is>
       </c>
-      <c r="C53" s="15" t="inlineStr">
+      <c r="C53" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="15" t="n">
+      <c r="A54" s="17" t="n">
         <v>51</v>
       </c>
-      <c r="B54" s="15" t="inlineStr">
+      <c r="B54" s="17" t="inlineStr">
         <is>
           <t>Construction of Hostels for OBC Boys and Girls</t>
         </is>
       </c>
-      <c r="C54" s="15" t="inlineStr">
+      <c r="C54" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="15" t="n">
+      <c r="A55" s="17" t="n">
         <v>52</v>
       </c>
-      <c r="B55" s="15" t="inlineStr">
+      <c r="B55" s="17" t="inlineStr">
         <is>
           <t>PM-YASASVI: Pre-Matric Scholarship for OBC, EBC and DNT Students</t>
         </is>
       </c>
-      <c r="C55" s="15" t="inlineStr">
+      <c r="C55" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="15" t="n">
+      <c r="A56" s="17" t="n">
         <v>53</v>
       </c>
-      <c r="B56" s="15" t="inlineStr">
+      <c r="B56" s="17" t="inlineStr">
         <is>
           <t>SMILE - Comprehensive Rehabilitation For Welfare Of Transgender Persons</t>
         </is>
       </c>
-      <c r="C56" s="15" t="inlineStr">
+      <c r="C56" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="15" t="n">
+      <c r="A57" s="17" t="n">
         <v>54</v>
       </c>
-      <c r="B57" s="15" t="inlineStr">
+      <c r="B57" s="17" t="inlineStr">
         <is>
           <t>PM-YASASVI: Top Class College Education for OBC, EBC and DNT Students</t>
         </is>
       </c>
-      <c r="C57" s="15" t="inlineStr">
+      <c r="C57" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="15" t="n">
+      <c r="A58" s="17" t="n">
         <v>55</v>
       </c>
-      <c r="B58" s="15" t="inlineStr">
+      <c r="B58" s="17" t="inlineStr">
         <is>
           <t>Micro Credit Finance (NSFDC)</t>
         </is>
       </c>
-      <c r="C58" s="15" t="inlineStr">
+      <c r="C58" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="15" t="n">
+      <c r="A59" s="17" t="n">
         <v>56</v>
       </c>
-      <c r="B59" s="15" t="inlineStr">
+      <c r="B59" s="17" t="inlineStr">
         <is>
           <t>Information, Monitoring, Evaluation and Social Audit (I-MESA): Evaluation and Studies</t>
         </is>
       </c>
-      <c r="C59" s="15" t="inlineStr">
+      <c r="C59" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="15" t="n">
+      <c r="A60" s="17" t="n">
         <v>57</v>
       </c>
-      <c r="B60" s="15" t="inlineStr">
+      <c r="B60" s="17" t="inlineStr">
         <is>
           <t>Scheme for Economic Empowerment of De-notified, Nomadic and Semi-Nomadic Tribes - "Educational Empowerment" Component</t>
         </is>
       </c>
-      <c r="C60" s="15" t="inlineStr">
+      <c r="C60" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="15" t="n">
+      <c r="A61" s="17" t="n">
         <v>58</v>
       </c>
-      <c r="B61" s="15" t="inlineStr">
+      <c r="B61" s="17" t="inlineStr">
         <is>
           <t>Gharaunda-Group Home for Adults Scheme</t>
         </is>
       </c>
-      <c r="C61" s="15" t="inlineStr">
+      <c r="C61" s="17" t="inlineStr">
         <is>
           <t>Dept. of Empowerment of Persons with Disabilities</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="15" t="n">
+      <c r="A62" s="17" t="n">
         <v>59</v>
       </c>
-      <c r="B62" s="15" t="inlineStr">
+      <c r="B62" s="17" t="inlineStr">
         <is>
           <t>National Award for Individual Excellence</t>
         </is>
       </c>
-      <c r="C62" s="15" t="inlineStr">
+      <c r="C62" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="15" t="n">
+      <c r="A63" s="17" t="n">
         <v>60</v>
       </c>
-      <c r="B63" s="15" t="inlineStr">
+      <c r="B63" s="17" t="inlineStr">
         <is>
           <t>Divyangjan Kaushal Yojana</t>
         </is>
       </c>
-      <c r="C63" s="15" t="inlineStr">
+      <c r="C63" s="17" t="inlineStr">
         <is>
           <t>Dept. of Empowerment of Persons with Disabilities</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="15" t="n">
+      <c r="A64" s="17" t="n">
         <v>61</v>
       </c>
-      <c r="B64" s="15" t="inlineStr">
+      <c r="B64" s="17" t="inlineStr">
         <is>
           <t>Dr. Ambedakar Centrally Sponsored Scheme of Post-Matric Scholarships for the Economically Backward Class (EBC) Students</t>
         </is>
       </c>
-      <c r="C64" s="15" t="inlineStr">
+      <c r="C64" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="15" t="n">
+      <c r="A65" s="17" t="n">
         <v>62</v>
       </c>
-      <c r="B65" s="15" t="inlineStr">
+      <c r="B65" s="17" t="inlineStr">
         <is>
           <t>Assistance to Voluntary Organizations Working for Welfare of OBCs</t>
         </is>
       </c>
-      <c r="C65" s="15" t="inlineStr">
+      <c r="C65" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="15" t="n">
+      <c r="A66" s="17" t="n">
         <v>63</v>
       </c>
-      <c r="B66" s="15" t="inlineStr">
+      <c r="B66" s="17" t="inlineStr">
         <is>
           <t>Self Employment Scheme For Rehabilitation Of Manual Scavengers</t>
         </is>
       </c>
-      <c r="C66" s="15" t="inlineStr">
+      <c r="C66" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="15" t="n">
+      <c r="A67" s="17" t="n">
         <v>64</v>
       </c>
-      <c r="B67" s="15" t="inlineStr">
+      <c r="B67" s="17" t="inlineStr">
         <is>
           <t>Loan Based Schemes For Safai Karamchari - General Term Loan (GTL)</t>
         </is>
       </c>
-      <c r="C67" s="15" t="inlineStr">
+      <c r="C67" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="15" t="n">
+      <c r="A68" s="17" t="n">
         <v>65</v>
       </c>
-      <c r="B68" s="15" t="inlineStr">
+      <c r="B68" s="17" t="inlineStr">
         <is>
           <t>Scheme for Supportive Money to the Parents of Transgender Children</t>
         </is>
       </c>
-      <c r="C68" s="15" t="inlineStr">
+      <c r="C68" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="15" t="n">
+      <c r="A69" s="17" t="n">
         <v>66</v>
       </c>
-      <c r="B69" s="15" t="inlineStr">
+      <c r="B69" s="17" t="inlineStr">
         <is>
           <t>Rashtriya Parivar Sahayata Yojana</t>
         </is>
       </c>
-      <c r="C69" s="15" t="inlineStr">
+      <c r="C69" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="15" t="n">
+      <c r="A70" s="17" t="n">
         <v>67</v>
       </c>
-      <c r="B70" s="15" t="inlineStr">
+      <c r="B70" s="17" t="inlineStr">
         <is>
           <t>Pradhan Mantri Adarsh Gram Yojana</t>
         </is>
       </c>
-      <c r="C70" s="15" t="inlineStr">
+      <c r="C70" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="15" t="n">
+      <c r="A71" s="17" t="n">
         <v>68</v>
       </c>
-      <c r="B71" s="15" t="inlineStr">
+      <c r="B71" s="17" t="inlineStr">
         <is>
           <t>National Awards For Empowerment Of Persons With Disabilities: Divyangjano Ke Liye Sarvshrestha Placement Agency</t>
         </is>
       </c>
-      <c r="C71" s="15" t="inlineStr">
+      <c r="C71" s="17" t="inlineStr">
         <is>
           <t>Dept. of Empowerment of Persons with Disabilities</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="15" t="n">
+      <c r="A72" s="17" t="n">
         <v>69</v>
       </c>
-      <c r="B72" s="15" t="inlineStr">
+      <c r="B72" s="17" t="inlineStr">
         <is>
           <t>Scheme of Assistance for the Prevention of Alcoholism &amp; Substance (Drugs) Abuse and for Social Defence Services: General Grant-in-Aid Programme</t>
         </is>
       </c>
-      <c r="C72" s="15" t="inlineStr">
+      <c r="C72" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="15" t="n">
+      <c r="A73" s="17" t="n">
         <v>70</v>
       </c>
-      <c r="B73" s="15" t="inlineStr">
+      <c r="B73" s="17" t="inlineStr">
         <is>
           <t>Credit Enhancement Guarantee Scheme For The Scheduled Castes</t>
         </is>
       </c>
-      <c r="C73" s="15" t="inlineStr">
+      <c r="C73" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="15" t="n">
+      <c r="A74" s="17" t="n">
         <v>71</v>
       </c>
-      <c r="B74" s="15" t="inlineStr">
+      <c r="B74" s="17" t="inlineStr">
         <is>
           <t>Education Loan Scheme (NSFDC)</t>
         </is>
       </c>
-      <c r="C74" s="15" t="inlineStr">
+      <c r="C74" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="15" t="n">
+      <c r="A75" s="17" t="n">
         <v>72</v>
       </c>
-      <c r="B75" s="15" t="inlineStr">
+      <c r="B75" s="17" t="inlineStr">
         <is>
           <t>Information, Monitoring, Evaluation and Social Audit (I-MESA): Central Smart Surveillance Unit (CSSU)</t>
         </is>
       </c>
-      <c r="C75" s="15" t="inlineStr">
+      <c r="C75" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="15" t="n">
+      <c r="A76" s="17" t="n">
         <v>73</v>
       </c>
-      <c r="B76" s="15" t="inlineStr">
+      <c r="B76" s="17" t="inlineStr">
         <is>
           <t>Loan Based Schemes For Safai Karamchari - Sanitary Marts Scheme</t>
         </is>
       </c>
-      <c r="C76" s="15" t="inlineStr">
+      <c r="C76" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="15" t="n">
+      <c r="A77" s="17" t="n">
         <v>74</v>
       </c>
-      <c r="B77" s="15" t="inlineStr">
+      <c r="B77" s="17" t="inlineStr">
         <is>
           <t>Scheme Of Assistance To Disabled Persons For Purchase/Fitting Of Aids/Appliances</t>
         </is>
       </c>
-      <c r="C77" s="15" t="inlineStr">
+      <c r="C77" s="17" t="inlineStr">
         <is>
           <t>Dept. of Empowerment of Persons with Disabilities</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="15" t="n">
+      <c r="A78" s="17" t="n">
         <v>75</v>
       </c>
-      <c r="B78" s="15" t="inlineStr">
+      <c r="B78" s="17" t="inlineStr">
         <is>
           <t>Pradhan Mantri Anusuchit Jaati Abhyuday Yojana (PM-AJAY) - Adarsh Gram</t>
         </is>
       </c>
-      <c r="C78" s="15" t="inlineStr">
+      <c r="C78" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="15" t="n">
+      <c r="A79" s="17" t="n">
         <v>76</v>
       </c>
-      <c r="B79" s="15" t="inlineStr">
+      <c r="B79" s="17" t="inlineStr">
         <is>
           <t>National Awards For Empowerment Of Persons With Disabilities: Sugamya Bharat Abhiyan</t>
         </is>
       </c>
-      <c r="C79" s="15" t="inlineStr">
+      <c r="C79" s="17" t="inlineStr">
         <is>
           <t>Dept. of Empowerment of Persons with Disabilities</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="15" t="n">
+      <c r="A80" s="17" t="n">
         <v>77</v>
       </c>
-      <c r="B80" s="15" t="inlineStr">
+      <c r="B80" s="17" t="inlineStr">
         <is>
           <t>Loan Based Schemes For Safai Karamchari - Swachhta Udyami Yojana</t>
         </is>
       </c>
-      <c r="C80" s="15" t="inlineStr">
+      <c r="C80" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="15" t="n">
+      <c r="A81" s="17" t="n">
         <v>78</v>
       </c>
-      <c r="B81" s="15" t="inlineStr">
+      <c r="B81" s="17" t="inlineStr">
         <is>
           <t>Credit Based Schemes For SC - Term Loan (TL)</t>
         </is>
       </c>
-      <c r="C81" s="15" t="inlineStr">
+      <c r="C81" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="15" t="n">
+      <c r="A82" s="17" t="n">
         <v>79</v>
       </c>
-      <c r="B82" s="15" t="inlineStr">
+      <c r="B82" s="17" t="inlineStr">
         <is>
           <t>National Awards For Empowerment Of Persons With Disabilities: Divyangjano Ke Liye Sarvshrestha Niyoktha</t>
         </is>
       </c>
-      <c r="C82" s="15" t="inlineStr">
+      <c r="C82" s="17" t="inlineStr">
         <is>
           <t>Dept. of Empowerment of Persons with Disabilities</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="15" t="n">
+      <c r="A83" s="17" t="n">
         <v>80</v>
       </c>
-      <c r="B83" s="15" t="inlineStr">
+      <c r="B83" s="17" t="inlineStr">
         <is>
           <t>National Awards For Empowerment Of Persons With Disabilities: Sarveshrestha Sansthan (Private Organization, NGO)</t>
         </is>
       </c>
-      <c r="C83" s="15" t="inlineStr">
+      <c r="C83" s="17" t="inlineStr">
         <is>
           <t>Dept. of Empowerment of Persons with Disabilities</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="15" t="n">
+      <c r="A84" s="17" t="n">
         <v>81</v>
       </c>
-      <c r="B84" s="15" t="inlineStr">
+      <c r="B84" s="17" t="inlineStr">
         <is>
           <t>Scheme of Grant-in-Aid to Voluntary and other Organizations Working for Scheduled Castes</t>
         </is>
       </c>
-      <c r="C84" s="15" t="inlineStr">
+      <c r="C84" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="15" t="n">
+      <c r="A85" s="17" t="n">
         <v>82</v>
       </c>
-      <c r="B85" s="15" t="inlineStr">
+      <c r="B85" s="17" t="inlineStr">
         <is>
           <t>National Action for Mechanised Sanitation Ecosystem (NAMASTE) - "Emergency Response Sanitation Unit (ERSU) Formation and Functionalisation"</t>
         </is>
       </c>
-      <c r="C85" s="15" t="inlineStr">
+      <c r="C85" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="15" t="n">
+      <c r="A86" s="17" t="n">
         <v>83</v>
       </c>
-      <c r="B86" s="15" t="inlineStr">
+      <c r="B86" s="17" t="inlineStr">
         <is>
           <t>Deen Dayal Disabled Rehabilitation Scheme</t>
         </is>
       </c>
-      <c r="C86" s="15" t="inlineStr">
+      <c r="C86" s="17" t="inlineStr">
         <is>
           <t>Dept. of Empowerment of Persons with Disabilities</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="15" t="n">
+      <c r="A87" s="17" t="n">
         <v>84</v>
       </c>
-      <c r="B87" s="15" t="inlineStr">
+      <c r="B87" s="17" t="inlineStr">
         <is>
           <t>Vanchit Ikai Samooh aur Vargon ki Aarthik Sahayata Yojana (VISVAS) for Self-Help Groups</t>
         </is>
       </c>
-      <c r="C87" s="15" t="inlineStr">
+      <c r="C87" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="15" t="n">
+      <c r="A88" s="17" t="n">
         <v>85</v>
       </c>
-      <c r="B88" s="15" t="inlineStr">
+      <c r="B88" s="17" t="inlineStr">
         <is>
           <t>Loan based Scheme for Pay and Use Community Toilets</t>
         </is>
       </c>
-      <c r="C88" s="15" t="inlineStr">
+      <c r="C88" s="17" t="inlineStr">
         <is>
           <t>Dept. of Social Justice &amp; Empowerment (or its corporations)</t>
         </is>
@@ -9614,13 +12127,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -9628,142 +12141,150 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>How every claim in this workbook was checked</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Short form used in the sheet</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>The document it refers to</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Annual Report 2025-26, ch.3</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Department of Social Justice and Empowerment, Annual Report 2025-26, Chapter 3 — socialjustice.gov.in/writereaddata/UploadFile/71441776233188.pdf</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Notes on Demands for Grants 2026-27, Demand No.93</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>Union Budget 2026-27, Notes on Demands for Grants, Demand No. 93 — indiabudget.gov.in/doc/eb/sbe93.pdf</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>PIB Year-End Review 2025</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>Press Information Bureau release 2209488, 29 December 2025</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>myScheme</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>myscheme.gov.in/search/ministry/Ministry Of Social Justice and Empowerment, and the individual scheme pages named in column J</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>organisation.json</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>apps/hub/src/content/website/organisation.json — the 228 organisation pages this site already publishes</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Record's own text</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>The body text of the page as published at the URL in column C, read on 9 September 2026</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>The tests applied</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>A record was counted as a scheme of this Department only where it appears in Chapter 3 of the Annual Report 2025-26, or carries a line in Demand No. 93 of the Notes on Demands for Grants 2026-27, or is a published scheme of the Dr. Ambedkar Foundation or the Babu Jagjivan Ram National Foundation, both bodies of this Department.</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="n"/>
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>A record was counted as a scheme of this Department only where it appears in Chapter 3 of the Annual Report 2025-26, or carries a line in Demand No. 93, or is a published scheme of the Dr. Ambedkar Foundation or the Babu Jagjivan Ram National Foundation, both bodies of this Department.</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>A record was counted as a State scheme only where its own text shows it: the page names the State, or uses a category name that only one State uses (VJNT and SBC are Maharashtra's; MBC is Tamil Nadu's; Gadia Lohar is a Rajasthan community). Nine of the 46 were then confirmed individually on myScheme, each published under a State — Maharashtra, Tamil Nadu or Rajasthan. None of the 46 appears in myScheme's list of Ministry schemes.</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="n"/>
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>A record was counted as a State scheme only where its own text shows it: the page names the State, or uses a category name that only one State uses (VJNT and SBC are Maharashtra's; MBC is Tamil Nadu's; Gadia Lohar is a Rajasthan community). Nine were confirmed individually on myScheme, each published under a State. None of the 46 appears in myScheme's Ministry list.</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>Where a State is marked '(inferred)', the page does not name the State and the attribution rests on category vocabulary alone. Those still need the Department's confirmation.</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="n"/>
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>Columns K and L were tagged by reading each record against the eleven personas and eight categories of the service-discovery model, taking the tags of the 38 canonical schemes from docs/research/dosje-scheme-master-2026-09.json where a record matches one, and reading the record's own text otherwise. A record may carry several of each.</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>Column J was matched by comparing scheme names. A match was accepted only at high similarity or where checked by hand; where the sheet says 'Not on myScheme in any form', that is the absence of a match, which is weaker evidence than a match — myScheme's coverage of this Department is itself incomplete (see the cross-check tab).</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="n"/>
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>Two categories marked PROPOSED do not exist in the model today. They were added because eleven and ten records respectively had no honest home in the existing eight.</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>Column J was matched by scheme name, accepted only at high similarity or by hand. 'Not on myScheme in any form' is an absence of a match, which is weaker evidence than a match — myScheme's coverage of this Department is itself incomplete.</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>This pass did not open the PDFs attached to each record, and did not test whether a scheme is still accepting applications.</t>
         </is>
       </c>
-      <c r="B16" s="15" t="n"/>
+      <c r="B17" s="17" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
